--- a/hall/resources/sample/popUpConfig.xlsx
+++ b/hall/resources/sample/popUpConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="popUpConfig" sheetId="1" r:id="rId1"/>
@@ -64,7 +64,30 @@
         </r>
       </text>
     </comment>
-    <comment ref="E1" authorId="0">
+    <comment ref="C1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+1：手机端
+2：webGL端</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="F1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -90,7 +113,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F1" authorId="0">
+    <comment ref="G1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -113,7 +136,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="N1" authorId="0">
+    <comment ref="O1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -135,7 +158,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="O1" authorId="0">
+    <comment ref="P1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -162,12 +185,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="105">
   <si>
     <t>序号ID</t>
   </si>
   <si>
     <t>弹窗类型值</t>
+  </si>
+  <si>
+    <t>弹窗对应平台</t>
   </si>
   <si>
     <t>#备注</t>
@@ -1158,7 +1184,7 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1203,6 +1229,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
@@ -1558,33 +1587,34 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:P14"/>
+  <dimension ref="A1:Q14"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="7.25" style="5" customWidth="1"/>
     <col min="2" max="2" width="30.75" style="5" customWidth="1"/>
-    <col min="3" max="3" width="35.5833333333333" style="5" customWidth="1"/>
-    <col min="4" max="4" width="14.625" style="5" customWidth="1"/>
-    <col min="5" max="5" width="57.375" style="6" customWidth="1"/>
-    <col min="6" max="6" width="72.35" style="5" customWidth="1"/>
-    <col min="7" max="7" width="48.525" style="4" customWidth="1"/>
-    <col min="8" max="8" width="12.875" style="4" customWidth="1"/>
-    <col min="9" max="9" width="16.25" style="5" customWidth="1"/>
-    <col min="10" max="10" width="8.875" style="5" customWidth="1"/>
-    <col min="11" max="11" width="20.8833333333333" style="7" customWidth="1"/>
-    <col min="12" max="12" width="21.175" style="7" customWidth="1"/>
-    <col min="13" max="15" width="12.875" style="8" customWidth="1"/>
-    <col min="16" max="16" width="72.125" style="5" customWidth="1"/>
-    <col min="17" max="17" width="9.375" style="5"/>
-    <col min="18" max="18" width="19.875" style="5" customWidth="1"/>
-    <col min="19" max="19" width="13.75" style="5" customWidth="1"/>
-    <col min="20" max="20" width="9" style="5"/>
-    <col min="21" max="21" width="9.375" style="5"/>
-    <col min="22" max="22" width="23.25" style="5" customWidth="1"/>
-    <col min="23" max="16384" width="9" style="5"/>
+    <col min="3" max="3" width="21.7583333333333" style="5" customWidth="1"/>
+    <col min="4" max="4" width="35.5833333333333" style="5" customWidth="1"/>
+    <col min="5" max="5" width="14.625" style="5" customWidth="1"/>
+    <col min="6" max="6" width="57.375" style="6" customWidth="1"/>
+    <col min="7" max="7" width="72.35" style="5" customWidth="1"/>
+    <col min="8" max="8" width="48.525" style="4" customWidth="1"/>
+    <col min="9" max="9" width="12.875" style="4" customWidth="1"/>
+    <col min="10" max="10" width="16.25" style="5" customWidth="1"/>
+    <col min="11" max="11" width="8.875" style="5" customWidth="1"/>
+    <col min="12" max="12" width="20.8833333333333" style="7" customWidth="1"/>
+    <col min="13" max="13" width="21.175" style="7" customWidth="1"/>
+    <col min="14" max="16" width="12.875" style="8" customWidth="1"/>
+    <col min="17" max="17" width="72.125" style="5" customWidth="1"/>
+    <col min="18" max="18" width="9.375" style="5"/>
+    <col min="19" max="19" width="19.875" style="5" customWidth="1"/>
+    <col min="20" max="20" width="13.75" style="5" customWidth="1"/>
+    <col min="21" max="21" width="9" style="5"/>
+    <col min="22" max="22" width="9.375" style="5"/>
+    <col min="23" max="23" width="23.25" style="5" customWidth="1"/>
+    <col min="24" max="16384" width="9" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" s="2" customFormat="1" ht="15" spans="1:16">
+    <row r="1" s="2" customFormat="1" ht="15" spans="1:17">
       <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
@@ -1597,31 +1627,31 @@
       <c r="D1" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="10" t="s">
+      <c r="E1" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="9" t="s">
+      <c r="F1" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="11" t="s">
+      <c r="G1" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="12" t="s">
+      <c r="H1" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="9" t="s">
+      <c r="I1" s="12" t="s">
         <v>8</v>
       </c>
       <c r="J1" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="13" t="s">
+      <c r="K1" s="9" t="s">
         <v>10</v>
       </c>
       <c r="L1" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="14" t="s">
+      <c r="M1" s="13" t="s">
         <v>12</v>
       </c>
       <c r="N1" s="14" t="s">
@@ -1630,91 +1660,93 @@
       <c r="O1" s="14" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" s="2" customFormat="1" ht="15" spans="1:16">
+      <c r="P1" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" s="2" customFormat="1" ht="15" spans="1:17">
       <c r="A2" s="9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B2" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="C2" s="16"/>
+      <c r="D2" s="9"/>
+      <c r="E2" s="9" t="s">
         <v>16</v>
-      </c>
-      <c r="C2" s="9"/>
-      <c r="D2" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="E2" s="15" t="s">
-        <v>17</v>
       </c>
       <c r="F2" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="G2" s="12" t="s">
-        <v>17</v>
+      <c r="G2" s="15" t="s">
+        <v>19</v>
       </c>
       <c r="H2" s="12" t="s">
-        <v>19</v>
-      </c>
-      <c r="I2" s="9" t="s">
-        <v>19</v>
+        <v>18</v>
+      </c>
+      <c r="I2" s="12" t="s">
+        <v>20</v>
       </c>
       <c r="J2" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="K2" s="13" t="s">
         <v>20</v>
       </c>
+      <c r="K2" s="9" t="s">
+        <v>20</v>
+      </c>
       <c r="L2" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="M2" s="14" t="s">
-        <v>15</v>
+        <v>21</v>
+      </c>
+      <c r="M2" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="N2" s="14" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="O2" s="14" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="3" s="2" customFormat="1" ht="15" spans="1:16">
+        <v>21</v>
+      </c>
+      <c r="P2" s="14" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="3" s="2" customFormat="1" ht="15" spans="1:17">
       <c r="A3" s="9" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C3" s="9"/>
-      <c r="D3" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="E3" s="10" t="s">
+      <c r="D3" s="9"/>
+      <c r="E3" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="F3" s="9" t="s">
+      <c r="F3" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="G3" s="11" t="s">
+      <c r="G3" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="H3" s="12" t="s">
+      <c r="H3" s="11" t="s">
         <v>27</v>
       </c>
-      <c r="I3" s="9" t="s">
+      <c r="I3" s="12" t="s">
         <v>28</v>
       </c>
       <c r="J3" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="K3" s="13" t="s">
+      <c r="K3" s="9" t="s">
         <v>30</v>
       </c>
       <c r="L3" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="M3" s="14" t="s">
+      <c r="M3" s="13" t="s">
         <v>32</v>
       </c>
       <c r="N3" s="14" t="s">
@@ -1723,452 +1755,456 @@
       <c r="O3" s="14" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="4" s="2" customFormat="1" ht="15" spans="1:16">
+      <c r="P3" s="14" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="4" s="2" customFormat="1" ht="15" spans="1:17">
       <c r="A4" s="9"/>
       <c r="B4" s="9"/>
       <c r="C4" s="9"/>
       <c r="D4" s="9"/>
-      <c r="E4" s="10"/>
-      <c r="F4" s="9"/>
-      <c r="G4" s="12"/>
+      <c r="E4" s="9"/>
+      <c r="F4" s="10"/>
+      <c r="G4" s="9"/>
       <c r="H4" s="12"/>
-      <c r="I4" s="9"/>
+      <c r="I4" s="12"/>
       <c r="J4" s="9"/>
-      <c r="K4" s="13"/>
+      <c r="K4" s="9"/>
       <c r="L4" s="13"/>
-      <c r="M4" s="14"/>
+      <c r="M4" s="13"/>
       <c r="N4" s="14"/>
       <c r="O4" s="14"/>
-    </row>
-    <row r="5" spans="1:16">
+      <c r="P4" s="14"/>
+    </row>
+    <row r="5" spans="1:17">
       <c r="A5" s="5">
         <v>1</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="C5" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="D5" s="5">
+      <c r="D5" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="E5" s="5">
         <v>3</v>
       </c>
-      <c r="F5" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="G5" s="4" t="s">
+      <c r="G5" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="H5" s="16" t="b">
+      <c r="H5" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="I5" s="17" t="b">
         <v>1</v>
       </c>
-      <c r="I5" s="17" t="b">
+      <c r="J5" s="18" t="b">
         <v>0</v>
       </c>
-      <c r="J5" s="16" t="b">
+      <c r="K5" s="17" t="b">
         <v>1</v>
       </c>
-      <c r="K5" s="25" t="s">
-        <v>39</v>
-      </c>
-      <c r="L5" s="25" t="s">
+      <c r="L5" s="26" t="s">
         <v>40</v>
       </c>
-      <c r="M5" s="8">
+      <c r="M5" s="26" t="s">
+        <v>41</v>
+      </c>
+      <c r="N5" s="8">
         <v>3</v>
       </c>
-      <c r="P5" s="5" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="6" s="3" customFormat="1" spans="1:16">
+      <c r="Q5" s="5" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="6" s="3" customFormat="1" spans="1:17">
       <c r="A6" s="3">
         <v>2</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="C6" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="D6" s="3">
+      <c r="D6" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="E6" s="3">
         <v>4</v>
       </c>
-      <c r="E6" s="18" t="s">
-        <v>44</v>
-      </c>
-      <c r="F6" s="3" t="s">
+      <c r="F6" s="19" t="s">
         <v>45</v>
       </c>
       <c r="G6" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="H6" s="17" t="b">
+      <c r="H6" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I6" s="18" t="b">
         <v>0</v>
       </c>
-      <c r="I6" s="17" t="b">
+      <c r="J6" s="18" t="b">
         <v>0</v>
       </c>
-      <c r="J6" s="17" t="b">
+      <c r="K6" s="18" t="b">
         <v>0</v>
       </c>
-      <c r="K6" s="26" t="s">
-        <v>39</v>
-      </c>
-      <c r="L6" s="26" t="s">
+      <c r="L6" s="27" t="s">
         <v>40</v>
       </c>
-      <c r="M6" s="20">
+      <c r="M6" s="27" t="s">
+        <v>41</v>
+      </c>
+      <c r="N6" s="21">
         <v>1</v>
       </c>
-      <c r="N6" s="20"/>
-      <c r="O6" s="20"/>
-      <c r="P6" s="3" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="7" s="4" customFormat="1" spans="1:16">
+      <c r="O6" s="21"/>
+      <c r="P6" s="21"/>
+      <c r="Q6" s="3" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="7" s="4" customFormat="1" spans="1:17">
       <c r="A7" s="4">
         <v>3</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="C7" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="D7" s="4">
+      <c r="D7" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="E7" s="4">
         <v>5</v>
       </c>
-      <c r="E7" s="21"/>
-      <c r="F7" s="4" t="s">
-        <v>49</v>
-      </c>
+      <c r="F7" s="22"/>
       <c r="G7" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="H7" s="16" t="b">
+      <c r="H7" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="I7" s="17" t="b">
         <v>1</v>
       </c>
-      <c r="I7" s="17" t="b">
+      <c r="J7" s="18" t="b">
         <v>0</v>
       </c>
-      <c r="J7" s="16" t="b">
+      <c r="K7" s="17" t="b">
         <v>1</v>
       </c>
-      <c r="K7" s="27" t="s">
-        <v>39</v>
-      </c>
-      <c r="L7" s="27" t="s">
+      <c r="L7" s="28" t="s">
         <v>40</v>
       </c>
-      <c r="M7" s="23">
+      <c r="M7" s="28" t="s">
+        <v>41</v>
+      </c>
+      <c r="N7" s="24">
         <v>5</v>
       </c>
-      <c r="N7" s="23"/>
-      <c r="O7" s="23"/>
-      <c r="P7" s="4" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="8" s="3" customFormat="1" spans="1:16">
+      <c r="O7" s="24"/>
+      <c r="P7" s="24"/>
+      <c r="Q7" s="4" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="8" s="3" customFormat="1" spans="1:17">
       <c r="A8" s="3">
         <v>4</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="C8" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="D8" s="3">
+      <c r="D8" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="E8" s="3">
         <v>6</v>
       </c>
-      <c r="E8" s="18"/>
-      <c r="F8" s="3" t="s">
-        <v>53</v>
-      </c>
+      <c r="F8" s="19"/>
       <c r="G8" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="H8" s="17" t="b">
+      <c r="H8" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="I8" s="18" t="b">
         <v>0</v>
       </c>
-      <c r="I8" s="17" t="b">
+      <c r="J8" s="18" t="b">
         <v>0</v>
       </c>
-      <c r="J8" s="17" t="b">
+      <c r="K8" s="18" t="b">
         <v>0</v>
       </c>
-      <c r="K8" s="26" t="s">
-        <v>39</v>
-      </c>
-      <c r="L8" s="26" t="s">
+      <c r="L8" s="27" t="s">
         <v>40</v>
       </c>
-      <c r="M8" s="20">
+      <c r="M8" s="27" t="s">
+        <v>41</v>
+      </c>
+      <c r="N8" s="21">
         <v>3</v>
       </c>
-      <c r="N8" s="20"/>
-      <c r="O8" s="20"/>
-      <c r="P8" s="3" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="9" s="3" customFormat="1" spans="1:16">
+      <c r="O8" s="21"/>
+      <c r="P8" s="21"/>
+      <c r="Q8" s="3" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="9" s="3" customFormat="1" spans="1:17">
       <c r="A9" s="3">
         <v>5</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="C9" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="D9" s="3">
+      <c r="D9" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="E9" s="3">
         <v>7</v>
       </c>
-      <c r="E9" s="18" t="s">
-        <v>57</v>
-      </c>
-      <c r="F9" s="3" t="s">
+      <c r="F9" s="19" t="s">
         <v>58</v>
       </c>
-      <c r="G9" s="17" t="s">
+      <c r="G9" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="H9" s="17" t="b">
+      <c r="H9" s="18" t="s">
+        <v>60</v>
+      </c>
+      <c r="I9" s="18" t="b">
         <v>0</v>
       </c>
-      <c r="I9" s="17" t="b">
+      <c r="J9" s="18" t="b">
         <v>0</v>
       </c>
-      <c r="J9" s="17" t="b">
+      <c r="K9" s="18" t="b">
         <v>0</v>
       </c>
-      <c r="K9" s="26" t="s">
-        <v>39</v>
-      </c>
-      <c r="L9" s="26" t="s">
-        <v>39</v>
-      </c>
-      <c r="M9" s="20">
+      <c r="L9" s="27" t="s">
+        <v>40</v>
+      </c>
+      <c r="M9" s="27" t="s">
+        <v>40</v>
+      </c>
+      <c r="N9" s="21">
         <v>2</v>
       </c>
-      <c r="N9" s="20"/>
-      <c r="O9" s="20"/>
-      <c r="P9" s="3" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="10" s="3" customFormat="1" spans="1:16">
+      <c r="O9" s="21"/>
+      <c r="P9" s="21"/>
+      <c r="Q9" s="3" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="10" s="3" customFormat="1" spans="1:17">
       <c r="A10" s="3">
         <v>6</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="C10" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="D10" s="3">
+      <c r="D10" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="E10" s="3">
         <v>8</v>
       </c>
-      <c r="E10" s="18"/>
-      <c r="F10" s="3"/>
+      <c r="F10" s="19"/>
       <c r="G10" s="3"/>
-      <c r="H10" s="17" t="b">
+      <c r="H10" s="3"/>
+      <c r="I10" s="18" t="b">
         <v>0</v>
       </c>
-      <c r="I10" s="17" t="b">
+      <c r="J10" s="18" t="b">
         <v>0</v>
       </c>
-      <c r="J10" s="17" t="b">
+      <c r="K10" s="18" t="b">
         <v>0</v>
       </c>
-      <c r="K10" s="26" t="s">
-        <v>39</v>
-      </c>
-      <c r="L10" s="26" t="s">
-        <v>62</v>
-      </c>
-      <c r="M10" s="20">
+      <c r="L10" s="27" t="s">
+        <v>40</v>
+      </c>
+      <c r="M10" s="27" t="s">
+        <v>63</v>
+      </c>
+      <c r="N10" s="21">
         <v>1</v>
       </c>
-      <c r="N10" s="20"/>
-      <c r="O10" s="20"/>
-      <c r="P10" s="3" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="11" s="3" customFormat="1" spans="1:16">
+      <c r="O10" s="21"/>
+      <c r="P10" s="21"/>
+      <c r="Q10" s="3" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="11" s="3" customFormat="1" spans="1:17">
       <c r="A11" s="3">
         <v>7</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="C11" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="D11" s="3">
+      <c r="D11" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="E11" s="3">
         <v>9</v>
       </c>
-      <c r="E11" s="18"/>
-      <c r="F11" s="3" t="s">
-        <v>65</v>
-      </c>
+      <c r="F11" s="19"/>
       <c r="G11" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="H11" s="17" t="b">
+      <c r="H11" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="I11" s="18" t="b">
         <v>0</v>
       </c>
-      <c r="I11" s="17" t="b">
+      <c r="J11" s="18" t="b">
         <v>0</v>
       </c>
-      <c r="J11" s="17" t="b">
+      <c r="K11" s="18" t="b">
         <v>0</v>
       </c>
-      <c r="K11" s="26" t="s">
-        <v>39</v>
-      </c>
-      <c r="L11" s="26" t="s">
-        <v>62</v>
-      </c>
-      <c r="M11" s="20">
+      <c r="L11" s="27" t="s">
+        <v>40</v>
+      </c>
+      <c r="M11" s="27" t="s">
+        <v>63</v>
+      </c>
+      <c r="N11" s="21">
         <v>3</v>
       </c>
-      <c r="N11" s="20"/>
-      <c r="O11" s="20"/>
-      <c r="P11" s="3" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="12" s="3" customFormat="1" spans="1:16">
+      <c r="O11" s="21"/>
+      <c r="P11" s="21"/>
+      <c r="Q11" s="3" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="12" s="3" customFormat="1" spans="1:17">
       <c r="A12" s="3">
         <v>8</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="C12" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="D12" s="3">
+      <c r="D12" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="E12" s="3">
         <v>10</v>
       </c>
-      <c r="E12" s="18"/>
-      <c r="F12" s="3"/>
+      <c r="F12" s="19"/>
       <c r="G12" s="3"/>
-      <c r="H12" s="17" t="b">
+      <c r="H12" s="3"/>
+      <c r="I12" s="18" t="b">
         <v>0</v>
       </c>
-      <c r="I12" s="17" t="b">
+      <c r="J12" s="18" t="b">
         <v>0</v>
       </c>
-      <c r="J12" s="17" t="b">
+      <c r="K12" s="18" t="b">
         <v>0</v>
       </c>
-      <c r="K12" s="26" t="s">
-        <v>39</v>
-      </c>
-      <c r="L12" s="26" t="s">
+      <c r="L12" s="27" t="s">
         <v>40</v>
       </c>
-      <c r="M12" s="20">
+      <c r="M12" s="27" t="s">
+        <v>41</v>
+      </c>
+      <c r="N12" s="21">
         <v>1</v>
       </c>
-      <c r="N12" s="20"/>
-      <c r="O12" s="20"/>
-      <c r="P12" s="3" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="13" s="3" customFormat="1" spans="1:16">
+      <c r="O12" s="21"/>
+      <c r="P12" s="21"/>
+      <c r="Q12" s="3" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="13" s="3" customFormat="1" spans="1:17">
       <c r="A13" s="3">
         <v>9</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="C13" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="D13" s="3">
+      <c r="D13" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="E13" s="3">
         <v>2</v>
       </c>
-      <c r="E13" s="18" t="s">
-        <v>71</v>
-      </c>
-      <c r="F13" s="18"/>
-      <c r="G13" s="3"/>
-      <c r="H13" s="17" t="b">
+      <c r="F13" s="19" t="s">
+        <v>72</v>
+      </c>
+      <c r="G13" s="19"/>
+      <c r="H13" s="3"/>
+      <c r="I13" s="18" t="b">
         <v>0</v>
       </c>
-      <c r="I13" s="17" t="b">
+      <c r="J13" s="18" t="b">
         <v>0</v>
       </c>
-      <c r="J13" s="17" t="b">
+      <c r="K13" s="18" t="b">
         <v>0</v>
       </c>
-      <c r="K13" s="26" t="s">
-        <v>72</v>
-      </c>
-      <c r="L13" s="26" t="s">
+      <c r="L13" s="27" t="s">
         <v>73</v>
       </c>
-      <c r="M13" s="20">
+      <c r="M13" s="27" t="s">
+        <v>74</v>
+      </c>
+      <c r="N13" s="21">
         <v>99</v>
       </c>
-      <c r="N13" s="24"/>
-      <c r="O13" s="18"/>
-      <c r="P13" s="3" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="14" s="4" customFormat="1" spans="1:16">
+      <c r="O13" s="25"/>
+      <c r="P13" s="19"/>
+      <c r="Q13" s="3" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="14" s="4" customFormat="1" spans="1:17">
       <c r="A14" s="4">
         <v>10</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="C14" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="D14" s="4">
+      <c r="D14" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="E14" s="4">
         <v>1</v>
       </c>
-      <c r="E14" s="21"/>
-      <c r="F14" s="4"/>
-      <c r="H14" s="16" t="b">
+      <c r="F14" s="22"/>
+      <c r="G14" s="4"/>
+      <c r="I14" s="17" t="b">
         <v>1</v>
       </c>
-      <c r="I14" s="17" t="b">
+      <c r="J14" s="18" t="b">
         <v>0</v>
       </c>
-      <c r="J14" s="16" t="b">
+      <c r="K14" s="17" t="b">
         <v>1</v>
       </c>
-      <c r="K14" s="27" t="s">
-        <v>72</v>
-      </c>
-      <c r="L14" s="27" t="s">
-        <v>77</v>
-      </c>
-      <c r="M14" s="23">
+      <c r="L14" s="28" t="s">
+        <v>73</v>
+      </c>
+      <c r="M14" s="28" t="s">
+        <v>78</v>
+      </c>
+      <c r="N14" s="24">
         <v>99</v>
       </c>
-      <c r="N14" s="23"/>
-      <c r="O14" s="23"/>
-      <c r="P14" s="4" t="s">
-        <v>78</v>
+      <c r="O14" s="24"/>
+      <c r="P14" s="24"/>
+      <c r="Q14" s="4" t="s">
+        <v>79</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="O13">
+  <conditionalFormatting sqref="P13">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2189,42 +2225,42 @@
   <sheetData>
     <row r="1" spans="1:16">
       <c r="A1" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="2" spans="1:16">
       <c r="A2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="3" spans="1:16">
       <c r="A3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="4" spans="1:16">
       <c r="A4" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="5" spans="1:16">
       <c r="A5" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="6" spans="1:16">
       <c r="A6" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="7" spans="1:16">
       <c r="A7" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="9" spans="1:16">
       <c r="A9" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B9" s="1"/>
       <c r="C9" s="1"/>
@@ -2247,20 +2283,20 @@
         <v>1</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D10" s="1">
         <v>1</v>
       </c>
       <c r="E10" s="1"/>
       <c r="F10" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H10" s="1"/>
       <c r="I10" s="1"/>
@@ -2277,20 +2313,20 @@
         <v>2</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D11" s="1">
         <v>2</v>
       </c>
       <c r="E11" s="1"/>
       <c r="F11" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H11" s="1"/>
       <c r="I11" s="1"/>
@@ -2307,20 +2343,20 @@
         <v>3</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D12" s="1">
         <v>4</v>
       </c>
       <c r="E12" s="1"/>
       <c r="F12" s="1" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="H12" s="1"/>
       <c r="I12" s="1"/>
@@ -2337,20 +2373,20 @@
         <v>4</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D13" s="1">
         <v>5</v>
       </c>
       <c r="E13" s="1"/>
       <c r="F13" s="1" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="H13" s="1"/>
       <c r="I13" s="1"/>
@@ -2367,22 +2403,22 @@
         <v>5</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D14" s="1">
         <v>3</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="H14" s="1"/>
       <c r="I14" s="1"/>
@@ -2399,10 +2435,10 @@
         <v>6</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D15" s="1">
         <v>6</v>
@@ -2425,17 +2461,17 @@
         <v>7</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D16" s="1">
         <v>7</v>
       </c>
       <c r="E16" s="1"/>
       <c r="F16" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G16" s="1"/>
       <c r="H16" s="1"/>

--- a/hall/resources/sample/popUpConfig.xlsx
+++ b/hall/resources/sample/popUpConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="popUpConfig" sheetId="1" r:id="rId1"/>
@@ -157,12 +157,35 @@
         </r>
       </text>
     </comment>
+    <comment ref="P1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+0-表示不出现可勾选的文字提示语
+1-表示出现可勾选的文字提示语，勾选后表示关闭该弹窗后当天不再弹出该弹窗</t>
+        </r>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="107">
   <si>
     <t>序号ID</t>
   </si>
@@ -209,6 +232,9 @@
     <t>帮助文本</t>
   </si>
   <si>
+    <t>弹窗提示语</t>
+  </si>
+  <si>
     <t>int</t>
   </si>
   <si>
@@ -269,6 +295,9 @@
     <t>help</t>
   </si>
   <si>
+    <t>Prompt</t>
+  </si>
+  <si>
     <t>4_106</t>
   </si>
   <si>
@@ -365,6 +394,12 @@
     <t>PlatformHall/UINotice/MVCHead</t>
   </si>
   <si>
+    <t>2025/12/1 0:00:00</t>
+  </si>
+  <si>
+    <t>2036/12/31 23:59:59</t>
+  </si>
+  <si>
     <t>19_121</t>
   </si>
   <si>
@@ -380,9 +415,6 @@
     <t>tanchuang_res/%s/tanchuang-test1.png</t>
   </si>
   <si>
-    <t>2025/12/1 0:00:00</t>
-  </si>
-  <si>
     <t>2025/12/31 23:59:59</t>
   </si>
   <si>
@@ -395,10 +427,10 @@
     <t>手机绑定弹窗</t>
   </si>
   <si>
-    <t>2036/12/31 23:59:59</t>
-  </si>
-  <si>
     <t>没有绑定手机号则弹出，绑定了就不弹出</t>
+  </si>
+  <si>
+    <t>https://j5wxcf.7mmon3ss.com/chatwindow.aspx?siteId=65002831&amp;planId=c245fbe6-4ec5-46d6-8542-657f871cc0b3</t>
   </si>
   <si>
     <t>每日奖金(原月卡)：UIDailyBonus</t>
@@ -486,7 +518,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="29">
+  <fonts count="30">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -535,6 +567,13 @@
       <u/>
       <sz val="11"/>
       <color theme="0" tint="-0.35"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1027,138 +1066,138 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1205,11 +1244,10 @@
     <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
@@ -1219,6 +1257,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
@@ -1228,7 +1267,7 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="6" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" quotePrefix="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="6" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" quotePrefix="1">
@@ -1558,7 +1597,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:P14"/>
+  <dimension ref="A1:Q15"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="7.25" style="5" customWidth="1"/>
@@ -1574,17 +1613,18 @@
     <col min="11" max="11" width="20.8833333333333" style="7" customWidth="1"/>
     <col min="12" max="12" width="21.175" style="7" customWidth="1"/>
     <col min="13" max="15" width="12.875" style="8" customWidth="1"/>
-    <col min="16" max="16" width="72.125" style="5" customWidth="1"/>
-    <col min="17" max="17" width="9.375" style="5"/>
-    <col min="18" max="18" width="19.875" style="5" customWidth="1"/>
-    <col min="19" max="19" width="13.75" style="5" customWidth="1"/>
-    <col min="20" max="20" width="9" style="5"/>
-    <col min="21" max="21" width="9.375" style="5"/>
-    <col min="22" max="22" width="23.25" style="5" customWidth="1"/>
-    <col min="23" max="16384" width="9" style="5"/>
+    <col min="16" max="16" width="13.2333333333333" style="5" customWidth="1"/>
+    <col min="17" max="17" width="72.125" style="5" customWidth="1"/>
+    <col min="18" max="18" width="9.375" style="5"/>
+    <col min="19" max="19" width="19.875" style="5" customWidth="1"/>
+    <col min="20" max="20" width="13.75" style="5" customWidth="1"/>
+    <col min="21" max="21" width="9" style="5"/>
+    <col min="22" max="22" width="9.375" style="5"/>
+    <col min="23" max="23" width="23.25" style="5" customWidth="1"/>
+    <col min="24" max="16384" width="9" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" s="2" customFormat="1" ht="15" spans="1:16">
+    <row r="1" s="2" customFormat="1" ht="15" spans="1:17">
       <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
@@ -1630,101 +1670,110 @@
       <c r="O1" s="14" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="2" t="s">
+      <c r="P1" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="2" s="2" customFormat="1" ht="15" spans="1:16">
+    <row r="2" s="2" customFormat="1" ht="15" spans="1:17">
       <c r="A2" s="9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B2" s="15" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C2" s="9"/>
       <c r="D2" s="9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E2" s="15" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F2" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="G2" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="G2" s="12" t="s">
-        <v>17</v>
-      </c>
       <c r="H2" s="12" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I2" s="9" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J2" s="9" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K2" s="13" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L2" s="13" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="M2" s="14" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="N2" s="14" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="O2" s="14" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="3" s="2" customFormat="1" ht="15" spans="1:16">
+        <v>16</v>
+      </c>
+      <c r="P2" s="14" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="3" s="2" customFormat="1" ht="15" spans="1:17">
       <c r="A3" s="9" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C3" s="9"/>
       <c r="D3" s="9" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E3" s="10" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F3" s="9" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G3" s="11" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H3" s="12" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="I3" s="9" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="J3" s="9" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K3" s="13" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="L3" s="13" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="M3" s="14" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="N3" s="14" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="O3" s="14" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="4" s="2" customFormat="1" ht="15" spans="1:16">
+        <v>35</v>
+      </c>
+      <c r="P3" s="14" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="4" s="2" customFormat="1" ht="15" spans="1:17">
       <c r="A4" s="9"/>
       <c r="B4" s="9"/>
       <c r="C4" s="9"/>
@@ -1740,157 +1789,162 @@
       <c r="M4" s="14"/>
       <c r="N4" s="14"/>
       <c r="O4" s="14"/>
-    </row>
-    <row r="5" spans="1:16">
-      <c r="A5" s="5">
+      <c r="P4" s="14"/>
+    </row>
+    <row r="5" s="3" customFormat="1" spans="1:17">
+      <c r="A5" s="3">
         <v>1</v>
       </c>
-      <c r="B5" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="D5" s="5">
+      <c r="B5" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="D5" s="3"/>
+      <c r="E5" s="16"/>
+      <c r="F5" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="H5" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="I5" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="J5" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="K5" s="26" t="s">
+        <v>41</v>
+      </c>
+      <c r="L5" s="26" t="s">
+        <v>42</v>
+      </c>
+      <c r="M5" s="19">
         <v>3</v>
       </c>
-      <c r="F5" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="G5" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="H5" s="16" t="b">
-        <v>1</v>
-      </c>
-      <c r="I5" s="17" t="b">
-        <v>0</v>
-      </c>
-      <c r="J5" s="16" t="b">
-        <v>1</v>
-      </c>
-      <c r="K5" s="25" t="s">
-        <v>39</v>
-      </c>
-      <c r="L5" s="25" t="s">
-        <v>40</v>
-      </c>
-      <c r="M5" s="8">
-        <v>3</v>
-      </c>
-      <c r="P5" s="5" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="6" s="3" customFormat="1" spans="1:16">
+      <c r="N5" s="19"/>
+      <c r="O5" s="19"/>
+      <c r="P5" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q5" s="3" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="6" s="3" customFormat="1" spans="1:17">
       <c r="A6" s="3">
         <v>2</v>
       </c>
       <c r="B6" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="D6" s="3"/>
+      <c r="E6" s="16" t="s">
+        <v>46</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="H6" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="I6" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="J6" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="K6" s="26" t="s">
+        <v>41</v>
+      </c>
+      <c r="L6" s="26" t="s">
         <v>42</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="M6" s="19">
+        <v>1</v>
+      </c>
+      <c r="N6" s="19"/>
+      <c r="O6" s="19"/>
+      <c r="P6" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="D6" s="3">
-        <v>4</v>
-      </c>
-      <c r="E6" s="18" t="s">
-        <v>44</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="G6" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="H6" s="17" t="b">
-        <v>0</v>
-      </c>
-      <c r="I6" s="17" t="b">
-        <v>0</v>
-      </c>
-      <c r="J6" s="17" t="b">
-        <v>0</v>
-      </c>
-      <c r="K6" s="26" t="s">
-        <v>39</v>
-      </c>
-      <c r="L6" s="26" t="s">
-        <v>40</v>
-      </c>
-      <c r="M6" s="20">
-        <v>1</v>
-      </c>
-      <c r="N6" s="20"/>
-      <c r="O6" s="20"/>
-      <c r="P6" s="3" t="s">
+    </row>
+    <row r="7" s="3" customFormat="1" spans="1:17">
+      <c r="A7" s="3">
+        <v>3</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="D7" s="3"/>
+      <c r="E7" s="16"/>
+      <c r="F7" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="H7" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="I7" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="J7" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="K7" s="26" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="7" s="4" customFormat="1" spans="1:16">
-      <c r="A7" s="4">
-        <v>3</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="D7" s="4">
+      <c r="L7" s="26" t="s">
+        <v>42</v>
+      </c>
+      <c r="M7" s="19">
         <v>5</v>
       </c>
-      <c r="E7" s="21"/>
-      <c r="F7" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="G7" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="H7" s="16" t="b">
-        <v>1</v>
-      </c>
-      <c r="I7" s="17" t="b">
-        <v>0</v>
-      </c>
-      <c r="J7" s="16" t="b">
-        <v>1</v>
-      </c>
-      <c r="K7" s="27" t="s">
-        <v>39</v>
-      </c>
-      <c r="L7" s="27" t="s">
-        <v>40</v>
-      </c>
-      <c r="M7" s="23">
-        <v>5</v>
-      </c>
-      <c r="N7" s="23"/>
-      <c r="O7" s="23"/>
-      <c r="P7" s="4" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="8" s="3" customFormat="1" spans="1:16">
+      <c r="N7" s="19"/>
+      <c r="O7" s="19"/>
+      <c r="P7" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q7" s="3" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="8" s="3" customFormat="1" spans="1:17">
       <c r="A8" s="3">
         <v>4</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="D8" s="3">
-        <v>6</v>
-      </c>
-      <c r="E8" s="18"/>
+        <v>54</v>
+      </c>
+      <c r="D8" s="3"/>
+      <c r="E8" s="16"/>
       <c r="F8" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="H8" s="17" t="b">
         <v>0</v>
@@ -1902,41 +1956,42 @@
         <v>0</v>
       </c>
       <c r="K8" s="26" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="L8" s="26" t="s">
-        <v>40</v>
-      </c>
-      <c r="M8" s="20">
+        <v>42</v>
+      </c>
+      <c r="M8" s="19">
         <v>3</v>
       </c>
-      <c r="N8" s="20"/>
-      <c r="O8" s="20"/>
-      <c r="P8" s="3" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="9" s="3" customFormat="1" spans="1:16">
+      <c r="N8" s="19"/>
+      <c r="O8" s="19"/>
+      <c r="P8" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="3" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="9" s="3" customFormat="1" spans="1:17">
       <c r="A9" s="3">
         <v>5</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="D9" s="3">
-        <v>7</v>
-      </c>
-      <c r="E9" s="18" t="s">
-        <v>57</v>
+        <v>58</v>
+      </c>
+      <c r="D9" s="3"/>
+      <c r="E9" s="16" t="s">
+        <v>59</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="G9" s="17" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="H9" s="17" t="b">
         <v>0</v>
@@ -1948,34 +2003,35 @@
         <v>0</v>
       </c>
       <c r="K9" s="26" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="L9" s="26" t="s">
-        <v>39</v>
-      </c>
-      <c r="M9" s="20">
+        <v>42</v>
+      </c>
+      <c r="M9" s="19">
         <v>2</v>
       </c>
-      <c r="N9" s="20"/>
-      <c r="O9" s="20"/>
-      <c r="P9" s="3" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="10" s="3" customFormat="1" spans="1:16">
+      <c r="N9" s="19"/>
+      <c r="O9" s="19"/>
+      <c r="P9" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q9" s="3" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="10" s="3" customFormat="1" spans="1:17">
       <c r="A10" s="3">
         <v>6</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="D10" s="3">
-        <v>8</v>
-      </c>
-      <c r="E10" s="18"/>
+        <v>63</v>
+      </c>
+      <c r="D10" s="3"/>
+      <c r="E10" s="16"/>
       <c r="F10" s="3"/>
       <c r="G10" s="3"/>
       <c r="H10" s="17" t="b">
@@ -1988,78 +2044,82 @@
         <v>0</v>
       </c>
       <c r="K10" s="26" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="L10" s="26" t="s">
-        <v>62</v>
-      </c>
-      <c r="M10" s="20">
+        <v>64</v>
+      </c>
+      <c r="M10" s="19">
         <v>1</v>
       </c>
-      <c r="N10" s="20"/>
-      <c r="O10" s="20"/>
-      <c r="P10" s="3" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="11" s="3" customFormat="1" spans="1:16">
-      <c r="A11" s="3">
+      <c r="N10" s="19"/>
+      <c r="O10" s="19"/>
+      <c r="P10" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q10" s="3" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="11" s="4" customFormat="1" spans="1:17">
+      <c r="A11" s="4">
         <v>7</v>
       </c>
-      <c r="B11" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="D11" s="3">
-        <v>9</v>
-      </c>
-      <c r="E11" s="18"/>
-      <c r="F11" s="3" t="s">
+      <c r="B11" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="G11" s="3" t="s">
+      <c r="C11" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="H11" s="17" t="b">
-        <v>0</v>
-      </c>
-      <c r="I11" s="17" t="b">
-        <v>0</v>
-      </c>
-      <c r="J11" s="17" t="b">
-        <v>0</v>
-      </c>
-      <c r="K11" s="26" t="s">
-        <v>39</v>
-      </c>
-      <c r="L11" s="26" t="s">
-        <v>62</v>
-      </c>
-      <c r="M11" s="20">
+      <c r="D11" s="4">
         <v>3</v>
       </c>
-      <c r="N11" s="20"/>
-      <c r="O11" s="20"/>
-      <c r="P11" s="3" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="12" s="3" customFormat="1" spans="1:16">
+      <c r="E11" s="20"/>
+      <c r="F11" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="G11" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="H11" s="21" t="b">
+        <v>1</v>
+      </c>
+      <c r="I11" s="21" t="b">
+        <v>0</v>
+      </c>
+      <c r="J11" s="21" t="b">
+        <v>1</v>
+      </c>
+      <c r="K11" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="L11" s="27" t="s">
+        <v>70</v>
+      </c>
+      <c r="M11" s="23">
+        <v>99</v>
+      </c>
+      <c r="N11" s="23"/>
+      <c r="O11" s="23"/>
+      <c r="P11" s="3">
+        <v>1</v>
+      </c>
+      <c r="Q11" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="12" s="3" customFormat="1" spans="1:17">
       <c r="A12" s="3">
         <v>8</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="D12" s="3">
-        <v>10</v>
-      </c>
-      <c r="E12" s="18"/>
+        <v>72</v>
+      </c>
+      <c r="D12" s="3"/>
+      <c r="E12" s="16"/>
       <c r="F12" s="3"/>
       <c r="G12" s="3"/>
       <c r="H12" s="17" t="b">
@@ -2072,37 +2132,38 @@
         <v>0</v>
       </c>
       <c r="K12" s="26" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="L12" s="26" t="s">
-        <v>40</v>
-      </c>
-      <c r="M12" s="20">
+        <v>42</v>
+      </c>
+      <c r="M12" s="19">
         <v>1</v>
       </c>
-      <c r="N12" s="20"/>
-      <c r="O12" s="20"/>
-      <c r="P12" s="3" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="13" s="3" customFormat="1" spans="1:16">
+      <c r="N12" s="19"/>
+      <c r="O12" s="19"/>
+      <c r="P12" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q12" s="3" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="13" s="3" customFormat="1" spans="1:17">
       <c r="A13" s="3">
         <v>9</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="D13" s="3">
-        <v>2</v>
-      </c>
-      <c r="E13" s="18" t="s">
-        <v>71</v>
-      </c>
-      <c r="F13" s="18"/>
+        <v>74</v>
+      </c>
+      <c r="D13" s="3"/>
+      <c r="E13" s="16" t="s">
+        <v>75</v>
+      </c>
+      <c r="F13" s="16"/>
       <c r="G13" s="3"/>
       <c r="H13" s="17" t="b">
         <v>0</v>
@@ -2114,63 +2175,121 @@
         <v>0</v>
       </c>
       <c r="K13" s="26" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="L13" s="26" t="s">
-        <v>73</v>
-      </c>
-      <c r="M13" s="20">
+        <v>76</v>
+      </c>
+      <c r="M13" s="19">
         <v>99</v>
       </c>
       <c r="N13" s="24"/>
-      <c r="O13" s="18"/>
-      <c r="P13" s="3" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="14" s="4" customFormat="1" spans="1:16">
+      <c r="O13" s="16"/>
+      <c r="P13" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="3" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="14" s="4" customFormat="1" spans="1:17">
       <c r="A14" s="4">
         <v>10</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="D14" s="4">
         <v>1</v>
       </c>
-      <c r="E14" s="21"/>
+      <c r="E14" s="20"/>
       <c r="F14" s="4"/>
-      <c r="H14" s="16" t="b">
+      <c r="H14" s="21" t="b">
         <v>1</v>
       </c>
       <c r="I14" s="17" t="b">
         <v>0</v>
       </c>
-      <c r="J14" s="16" t="b">
+      <c r="J14" s="21" t="b">
         <v>1</v>
       </c>
       <c r="K14" s="27" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="L14" s="27" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="M14" s="23">
         <v>99</v>
       </c>
       <c r="N14" s="23"/>
       <c r="O14" s="23"/>
-      <c r="P14" s="4" t="s">
-        <v>78</v>
+      <c r="P14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="4" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="15" s="4" customFormat="1" spans="1:17">
+      <c r="A15" s="4">
+        <v>11</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="D15" s="4">
+        <v>2</v>
+      </c>
+      <c r="E15" s="20" t="s">
+        <v>75</v>
+      </c>
+      <c r="F15" s="20"/>
+      <c r="H15" s="21" t="b">
+        <v>1</v>
+      </c>
+      <c r="I15" s="21" t="b">
+        <v>0</v>
+      </c>
+      <c r="J15" s="21" t="b">
+        <v>1</v>
+      </c>
+      <c r="K15" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="L15" s="27" t="s">
+        <v>70</v>
+      </c>
+      <c r="M15" s="23">
+        <v>99</v>
+      </c>
+      <c r="N15" s="25" t="s">
+        <v>81</v>
+      </c>
+      <c r="O15" s="20"/>
+      <c r="P15" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q15" s="4" t="s">
+        <v>77</v>
       </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="O13">
+    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="O15">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
+  <hyperlinks>
+    <hyperlink ref="N15" r:id="rId3" display="https://j5wxcf.7mmon3ss.com/chatwindow.aspx?siteId=65002831&amp;planId=c245fbe6-4ec5-46d6-8542-657f871cc0b3"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>
@@ -2189,42 +2308,42 @@
   <sheetData>
     <row r="1" spans="1:16">
       <c r="A1" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
     </row>
     <row r="2" spans="1:16">
       <c r="A2" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
     </row>
     <row r="3" spans="1:16">
       <c r="A3" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
     </row>
     <row r="4" spans="1:16">
       <c r="A4" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
     </row>
     <row r="5" spans="1:16">
       <c r="A5" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
     </row>
     <row r="6" spans="1:16">
       <c r="A6" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
     </row>
     <row r="7" spans="1:16">
       <c r="A7" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
     </row>
     <row r="9" spans="1:16">
       <c r="A9" s="1" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="B9" s="1"/>
       <c r="C9" s="1"/>
@@ -2247,20 +2366,20 @@
         <v>1</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D10" s="1">
         <v>1</v>
       </c>
       <c r="E10" s="1"/>
       <c r="F10" s="1" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="H10" s="1"/>
       <c r="I10" s="1"/>
@@ -2277,20 +2396,20 @@
         <v>2</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="D11" s="1">
         <v>2</v>
       </c>
       <c r="E11" s="1"/>
       <c r="F11" s="1" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="H11" s="1"/>
       <c r="I11" s="1"/>
@@ -2307,20 +2426,20 @@
         <v>3</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="D12" s="1">
         <v>4</v>
       </c>
       <c r="E12" s="1"/>
       <c r="F12" s="1" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="H12" s="1"/>
       <c r="I12" s="1"/>
@@ -2337,20 +2456,20 @@
         <v>4</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D13" s="1">
         <v>5</v>
       </c>
       <c r="E13" s="1"/>
       <c r="F13" s="1" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="H13" s="1"/>
       <c r="I13" s="1"/>
@@ -2367,22 +2486,22 @@
         <v>5</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="D14" s="1">
         <v>3</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="H14" s="1"/>
       <c r="I14" s="1"/>
@@ -2399,10 +2518,10 @@
         <v>6</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="D15" s="1">
         <v>6</v>
@@ -2425,17 +2544,17 @@
         <v>7</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="D16" s="1">
         <v>7</v>
       </c>
       <c r="E16" s="1"/>
       <c r="F16" s="1" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="G16" s="1"/>
       <c r="H16" s="1"/>

--- a/hall/resources/sample/popUpConfig.xlsx
+++ b/hall/resources/sample/popUpConfig.xlsx
@@ -2085,7 +2085,7 @@
         <v>1</v>
       </c>
       <c r="I11" s="21" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J11" s="21" t="b">
         <v>1</v>

--- a/hall/resources/sample/popUpConfig.xlsx
+++ b/hall/resources/sample/popUpConfig.xlsx
@@ -185,7 +185,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="103">
   <si>
     <t>序号ID</t>
   </si>
@@ -325,9 +325,6 @@
     <t>每日奖金;摇钱树;签到奖励</t>
   </si>
   <si>
-    <t>tanchuang_res/%s/tc_mrjj_1.png;0;0</t>
-  </si>
-  <si>
     <t>UIDailyBonus_0;UICashCow_0;UISignIn_0</t>
   </si>
   <si>
@@ -364,9 +361,6 @@
     <t>商城;成长基金</t>
   </si>
   <si>
-    <t>tanchuang_res/%s/tc_sc_1.png;tanchuang_res/%s/tc_czjj_1.png</t>
-  </si>
-  <si>
     <t>UIMall_0;UIGoldFund_0</t>
   </si>
   <si>
@@ -412,9 +406,6 @@
     <t>纯弹窗&amp;外部链接</t>
   </si>
   <si>
-    <t>tanchuang_res/%s/tanchuang-test1.png</t>
-  </si>
-  <si>
     <t>2025/12/31 23:59:59</t>
   </si>
   <si>
@@ -428,9 +419,6 @@
   </si>
   <si>
     <t>没有绑定手机号则弹出，绑定了就不弹出</t>
-  </si>
-  <si>
-    <t>https://j5wxcf.7mmon3ss.com/chatwindow.aspx?siteId=65002831&amp;planId=c245fbe6-4ec5-46d6-8542-657f871cc0b3</t>
   </si>
   <si>
     <t>每日奖金(原月卡)：UIDailyBonus</t>
@@ -518,7 +506,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="30">
+  <fonts count="29">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -535,12 +523,12 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0" tint="-0.35"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
+      <color theme="0" tint="-0.35"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
@@ -567,13 +555,6 @@
       <u/>
       <sz val="11"/>
       <color theme="0" tint="-0.35"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1066,138 +1047,138 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1248,6 +1229,7 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
@@ -1257,7 +1239,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
@@ -1265,9 +1246,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="6" applyNumberFormat="1" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="6" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" quotePrefix="1">
@@ -1606,8 +1584,8 @@
     <col min="4" max="4" width="14.625" style="5" customWidth="1"/>
     <col min="5" max="5" width="57.375" style="6" customWidth="1"/>
     <col min="6" max="6" width="72.35" style="5" customWidth="1"/>
-    <col min="7" max="7" width="48.525" style="4" customWidth="1"/>
-    <col min="8" max="8" width="12.875" style="4" customWidth="1"/>
+    <col min="7" max="7" width="48.525" style="3" customWidth="1"/>
+    <col min="8" max="8" width="12.875" style="3" customWidth="1"/>
     <col min="9" max="9" width="16.25" style="5" customWidth="1"/>
     <col min="10" max="10" width="8.875" style="5" customWidth="1"/>
     <col min="11" max="11" width="20.8833333333333" style="7" customWidth="1"/>
@@ -1801,7 +1779,9 @@
       <c r="C5" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="D5" s="3"/>
+      <c r="D5" s="3">
+        <v>2</v>
+      </c>
       <c r="E5" s="16"/>
       <c r="F5" s="3" t="s">
         <v>39</v>
@@ -1810,25 +1790,25 @@
         <v>40</v>
       </c>
       <c r="H5" s="17" t="b">
-        <v>0</v>
-      </c>
-      <c r="I5" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="I5" s="18" t="b">
         <v>0</v>
       </c>
       <c r="J5" s="17" t="b">
-        <v>0</v>
-      </c>
-      <c r="K5" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="K5" s="25" t="s">
         <v>41</v>
       </c>
-      <c r="L5" s="26" t="s">
+      <c r="L5" s="25" t="s">
         <v>42</v>
       </c>
-      <c r="M5" s="19">
-        <v>3</v>
-      </c>
-      <c r="N5" s="19"/>
-      <c r="O5" s="19"/>
+      <c r="M5" s="20">
+        <v>99</v>
+      </c>
+      <c r="N5" s="20"/>
+      <c r="O5" s="20"/>
       <c r="P5" s="3">
         <v>0</v>
       </c>
@@ -1846,36 +1826,36 @@
       <c r="C6" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="D6" s="3"/>
-      <c r="E6" s="16" t="s">
+      <c r="D6" s="3">
+        <v>3</v>
+      </c>
+      <c r="E6" s="16"/>
+      <c r="F6" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="F6" s="3" t="s">
+      <c r="G6" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="G6" s="3" t="s">
-        <v>48</v>
-      </c>
       <c r="H6" s="17" t="b">
-        <v>0</v>
-      </c>
-      <c r="I6" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="I6" s="18" t="b">
         <v>0</v>
       </c>
       <c r="J6" s="17" t="b">
-        <v>0</v>
-      </c>
-      <c r="K6" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="K6" s="25" t="s">
         <v>41</v>
       </c>
-      <c r="L6" s="26" t="s">
+      <c r="L6" s="25" t="s">
         <v>42</v>
       </c>
-      <c r="M6" s="19">
-        <v>1</v>
-      </c>
-      <c r="N6" s="19"/>
-      <c r="O6" s="19"/>
+      <c r="M6" s="20">
+        <v>99</v>
+      </c>
+      <c r="N6" s="20"/>
+      <c r="O6" s="20"/>
       <c r="P6" s="3">
         <v>0</v>
       </c>
@@ -1888,39 +1868,41 @@
         <v>3</v>
       </c>
       <c r="B7" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="C7" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="C7" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="D7" s="3"/>
+      <c r="D7" s="3">
+        <v>4</v>
+      </c>
       <c r="E7" s="16"/>
       <c r="F7" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="G7" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="G7" s="3" t="s">
-        <v>52</v>
-      </c>
       <c r="H7" s="17" t="b">
-        <v>0</v>
-      </c>
-      <c r="I7" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="I7" s="18" t="b">
         <v>0</v>
       </c>
       <c r="J7" s="17" t="b">
-        <v>0</v>
-      </c>
-      <c r="K7" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="K7" s="25" t="s">
         <v>41</v>
       </c>
-      <c r="L7" s="26" t="s">
+      <c r="L7" s="25" t="s">
         <v>42</v>
       </c>
-      <c r="M7" s="19">
-        <v>5</v>
-      </c>
-      <c r="N7" s="19"/>
-      <c r="O7" s="19"/>
+      <c r="M7" s="20">
+        <v>99</v>
+      </c>
+      <c r="N7" s="20"/>
+      <c r="O7" s="20"/>
       <c r="P7" s="3">
         <v>0</v>
       </c>
@@ -1928,31 +1910,31 @@
         <v>43</v>
       </c>
     </row>
-    <row r="8" s="3" customFormat="1" spans="1:17">
-      <c r="A8" s="3">
+    <row r="8" s="4" customFormat="1" spans="1:17">
+      <c r="A8" s="4">
         <v>4</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B8" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="C8" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="D8" s="4"/>
+      <c r="E8" s="21"/>
+      <c r="F8" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="D8" s="3"/>
-      <c r="E8" s="16"/>
-      <c r="F8" s="3" t="s">
+      <c r="G8" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="G8" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="H8" s="17" t="b">
-        <v>0</v>
-      </c>
-      <c r="I8" s="17" t="b">
-        <v>0</v>
-      </c>
-      <c r="J8" s="17" t="b">
+      <c r="H8" s="18" t="b">
+        <v>0</v>
+      </c>
+      <c r="I8" s="18" t="b">
+        <v>0</v>
+      </c>
+      <c r="J8" s="18" t="b">
         <v>0</v>
       </c>
       <c r="K8" s="26" t="s">
@@ -1961,45 +1943,43 @@
       <c r="L8" s="26" t="s">
         <v>42</v>
       </c>
-      <c r="M8" s="19">
+      <c r="M8" s="23">
         <v>3</v>
       </c>
-      <c r="N8" s="19"/>
-      <c r="O8" s="19"/>
-      <c r="P8" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q8" s="3" t="s">
+      <c r="N8" s="23"/>
+      <c r="O8" s="23"/>
+      <c r="P8" s="4">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="4" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="9" s="3" customFormat="1" spans="1:17">
-      <c r="A9" s="3">
+    <row r="9" s="4" customFormat="1" spans="1:17">
+      <c r="A9" s="4">
         <v>5</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B9" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="C9" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="D9" s="4"/>
+      <c r="E9" s="21"/>
+      <c r="F9" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="D9" s="3"/>
-      <c r="E9" s="16" t="s">
+      <c r="G9" s="18" t="s">
         <v>59</v>
       </c>
-      <c r="F9" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="G9" s="17" t="s">
-        <v>61</v>
-      </c>
-      <c r="H9" s="17" t="b">
-        <v>0</v>
-      </c>
-      <c r="I9" s="17" t="b">
-        <v>0</v>
-      </c>
-      <c r="J9" s="17" t="b">
+      <c r="H9" s="18" t="b">
+        <v>0</v>
+      </c>
+      <c r="I9" s="18" t="b">
+        <v>0</v>
+      </c>
+      <c r="J9" s="18" t="b">
         <v>0</v>
       </c>
       <c r="K9" s="26" t="s">
@@ -2008,56 +1988,56 @@
       <c r="L9" s="26" t="s">
         <v>42</v>
       </c>
-      <c r="M9" s="19">
+      <c r="M9" s="23">
         <v>2</v>
       </c>
-      <c r="N9" s="19"/>
-      <c r="O9" s="19"/>
-      <c r="P9" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q9" s="3" t="s">
+      <c r="N9" s="23"/>
+      <c r="O9" s="23"/>
+      <c r="P9" s="4">
+        <v>0</v>
+      </c>
+      <c r="Q9" s="4" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="10" s="3" customFormat="1" spans="1:17">
-      <c r="A10" s="3">
+    <row r="10" s="4" customFormat="1" spans="1:17">
+      <c r="A10" s="4">
         <v>6</v>
       </c>
-      <c r="B10" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="D10" s="3"/>
-      <c r="E10" s="16"/>
-      <c r="F10" s="3"/>
-      <c r="G10" s="3"/>
-      <c r="H10" s="17" t="b">
-        <v>0</v>
-      </c>
-      <c r="I10" s="17" t="b">
-        <v>0</v>
-      </c>
-      <c r="J10" s="17" t="b">
+      <c r="B10" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="D10" s="4"/>
+      <c r="E10" s="21"/>
+      <c r="F10" s="4"/>
+      <c r="G10" s="4"/>
+      <c r="H10" s="18" t="b">
+        <v>0</v>
+      </c>
+      <c r="I10" s="18" t="b">
+        <v>0</v>
+      </c>
+      <c r="J10" s="18" t="b">
         <v>0</v>
       </c>
       <c r="K10" s="26" t="s">
         <v>41</v>
       </c>
       <c r="L10" s="26" t="s">
-        <v>64</v>
-      </c>
-      <c r="M10" s="19">
+        <v>62</v>
+      </c>
+      <c r="M10" s="23">
         <v>1</v>
       </c>
-      <c r="N10" s="19"/>
-      <c r="O10" s="19"/>
-      <c r="P10" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q10" s="3" t="s">
+      <c r="N10" s="23"/>
+      <c r="O10" s="23"/>
+      <c r="P10" s="4">
+        <v>0</v>
+      </c>
+      <c r="Q10" s="4" t="s">
         <v>43</v>
       </c>
     </row>
@@ -2066,69 +2046,67 @@
         <v>7</v>
       </c>
       <c r="B11" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="D11" s="4"/>
+      <c r="E11" s="21"/>
+      <c r="F11" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="C11" s="4" t="s">
+      <c r="G11" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="D11" s="4">
-        <v>3</v>
-      </c>
-      <c r="E11" s="20"/>
-      <c r="F11" s="4" t="s">
+      <c r="H11" s="18" t="b">
+        <v>0</v>
+      </c>
+      <c r="I11" s="18" t="b">
+        <v>0</v>
+      </c>
+      <c r="J11" s="18" t="b">
+        <v>0</v>
+      </c>
+      <c r="K11" s="26" t="s">
         <v>67</v>
       </c>
-      <c r="G11" s="4" t="s">
+      <c r="L11" s="26" t="s">
         <v>68</v>
-      </c>
-      <c r="H11" s="21" t="b">
-        <v>1</v>
-      </c>
-      <c r="I11" s="21" t="b">
-        <v>1</v>
-      </c>
-      <c r="J11" s="21" t="b">
-        <v>1</v>
-      </c>
-      <c r="K11" s="27" t="s">
-        <v>69</v>
-      </c>
-      <c r="L11" s="27" t="s">
-        <v>70</v>
       </c>
       <c r="M11" s="23">
         <v>99</v>
       </c>
       <c r="N11" s="23"/>
       <c r="O11" s="23"/>
-      <c r="P11" s="3">
+      <c r="P11" s="4">
         <v>1</v>
       </c>
       <c r="Q11" s="4" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="12" s="3" customFormat="1" spans="1:17">
-      <c r="A12" s="3">
+    <row r="12" s="4" customFormat="1" spans="1:17">
+      <c r="A12" s="4">
         <v>8</v>
       </c>
-      <c r="B12" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="D12" s="3"/>
-      <c r="E12" s="16"/>
-      <c r="F12" s="3"/>
-      <c r="G12" s="3"/>
-      <c r="H12" s="17" t="b">
-        <v>0</v>
-      </c>
-      <c r="I12" s="17" t="b">
-        <v>0</v>
-      </c>
-      <c r="J12" s="17" t="b">
+      <c r="B12" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="D12" s="4"/>
+      <c r="E12" s="21"/>
+      <c r="F12" s="4"/>
+      <c r="G12" s="4"/>
+      <c r="H12" s="18" t="b">
+        <v>0</v>
+      </c>
+      <c r="I12" s="18" t="b">
+        <v>0</v>
+      </c>
+      <c r="J12" s="18" t="b">
         <v>0</v>
       </c>
       <c r="K12" s="26" t="s">
@@ -2137,101 +2115,99 @@
       <c r="L12" s="26" t="s">
         <v>42</v>
       </c>
-      <c r="M12" s="19">
+      <c r="M12" s="23">
         <v>1</v>
       </c>
-      <c r="N12" s="19"/>
-      <c r="O12" s="19"/>
-      <c r="P12" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q12" s="3" t="s">
+      <c r="N12" s="23"/>
+      <c r="O12" s="23"/>
+      <c r="P12" s="4">
+        <v>0</v>
+      </c>
+      <c r="Q12" s="4" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="13" s="3" customFormat="1" spans="1:17">
-      <c r="A13" s="3">
+    <row r="13" s="4" customFormat="1" spans="1:17">
+      <c r="A13" s="4">
         <v>9</v>
       </c>
-      <c r="B13" s="3" t="s">
+      <c r="B13" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="D13" s="4"/>
+      <c r="E13" s="21"/>
+      <c r="F13" s="21"/>
+      <c r="G13" s="4"/>
+      <c r="H13" s="18" t="b">
+        <v>0</v>
+      </c>
+      <c r="I13" s="18" t="b">
+        <v>0</v>
+      </c>
+      <c r="J13" s="18" t="b">
+        <v>0</v>
+      </c>
+      <c r="K13" s="26" t="s">
+        <v>67</v>
+      </c>
+      <c r="L13" s="26" t="s">
         <v>73</v>
       </c>
-      <c r="C13" s="3" t="s">
+      <c r="M13" s="23">
+        <v>99</v>
+      </c>
+      <c r="N13" s="24"/>
+      <c r="O13" s="21"/>
+      <c r="P13" s="4">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="D13" s="3"/>
-      <c r="E13" s="16" t="s">
+    </row>
+    <row r="14" s="3" customFormat="1" spans="1:17">
+      <c r="A14" s="3">
+        <v>10</v>
+      </c>
+      <c r="B14" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="F13" s="16"/>
-      <c r="G13" s="3"/>
-      <c r="H13" s="17" t="b">
-        <v>0</v>
-      </c>
-      <c r="I13" s="17" t="b">
-        <v>0</v>
-      </c>
-      <c r="J13" s="17" t="b">
-        <v>0</v>
-      </c>
-      <c r="K13" s="26" t="s">
-        <v>69</v>
-      </c>
-      <c r="L13" s="26" t="s">
+      <c r="C14" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="M13" s="19">
+      <c r="D14" s="3">
+        <v>1</v>
+      </c>
+      <c r="E14" s="16"/>
+      <c r="F14" s="3"/>
+      <c r="H14" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="I14" s="18" t="b">
+        <v>0</v>
+      </c>
+      <c r="J14" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="K14" s="25" t="s">
+        <v>67</v>
+      </c>
+      <c r="L14" s="25" t="s">
+        <v>68</v>
+      </c>
+      <c r="M14" s="20">
         <v>99</v>
       </c>
-      <c r="N13" s="24"/>
-      <c r="O13" s="16"/>
-      <c r="P13" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q13" s="3" t="s">
+      <c r="N14" s="20"/>
+      <c r="O14" s="20"/>
+      <c r="P14" s="4">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="3" t="s">
         <v>77</v>
-      </c>
-    </row>
-    <row r="14" s="4" customFormat="1" spans="1:17">
-      <c r="A14" s="4">
-        <v>10</v>
-      </c>
-      <c r="B14" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="C14" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="D14" s="4">
-        <v>1</v>
-      </c>
-      <c r="E14" s="20"/>
-      <c r="F14" s="4"/>
-      <c r="H14" s="21" t="b">
-        <v>1</v>
-      </c>
-      <c r="I14" s="17" t="b">
-        <v>0</v>
-      </c>
-      <c r="J14" s="21" t="b">
-        <v>1</v>
-      </c>
-      <c r="K14" s="27" t="s">
-        <v>69</v>
-      </c>
-      <c r="L14" s="27" t="s">
-        <v>70</v>
-      </c>
-      <c r="M14" s="23">
-        <v>99</v>
-      </c>
-      <c r="N14" s="23"/>
-      <c r="O14" s="23"/>
-      <c r="P14" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q14" s="4" t="s">
-        <v>80</v>
       </c>
     </row>
     <row r="15" s="4" customFormat="1" spans="1:17">
@@ -2239,45 +2215,39 @@
         <v>11</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="D15" s="4">
-        <v>2</v>
-      </c>
-      <c r="E15" s="20" t="s">
-        <v>75</v>
-      </c>
-      <c r="F15" s="20"/>
-      <c r="H15" s="21" t="b">
-        <v>1</v>
-      </c>
-      <c r="I15" s="21" t="b">
-        <v>0</v>
-      </c>
-      <c r="J15" s="21" t="b">
-        <v>1</v>
-      </c>
-      <c r="K15" s="27" t="s">
-        <v>69</v>
-      </c>
-      <c r="L15" s="27" t="s">
-        <v>70</v>
+        <v>72</v>
+      </c>
+      <c r="D15" s="4"/>
+      <c r="E15" s="21"/>
+      <c r="F15" s="21"/>
+      <c r="H15" s="18" t="b">
+        <v>0</v>
+      </c>
+      <c r="I15" s="18" t="b">
+        <v>0</v>
+      </c>
+      <c r="J15" s="18" t="b">
+        <v>0</v>
+      </c>
+      <c r="K15" s="26" t="s">
+        <v>67</v>
+      </c>
+      <c r="L15" s="26" t="s">
+        <v>68</v>
       </c>
       <c r="M15" s="23">
         <v>99</v>
       </c>
-      <c r="N15" s="25" t="s">
-        <v>81</v>
-      </c>
-      <c r="O15" s="20"/>
-      <c r="P15" s="3">
+      <c r="N15" s="24"/>
+      <c r="O15" s="21"/>
+      <c r="P15" s="4">
         <v>0</v>
       </c>
       <c r="Q15" s="4" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
     </row>
   </sheetData>
@@ -2287,9 +2257,6 @@
   <conditionalFormatting sqref="O15">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
-  <hyperlinks>
-    <hyperlink ref="N15" r:id="rId3" display="https://j5wxcf.7mmon3ss.com/chatwindow.aspx?siteId=65002831&amp;planId=c245fbe6-4ec5-46d6-8542-657f871cc0b3"/>
-  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>
@@ -2308,42 +2275,42 @@
   <sheetData>
     <row r="1" spans="1:16">
       <c r="A1" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
     </row>
     <row r="2" spans="1:16">
       <c r="A2" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
     </row>
     <row r="3" spans="1:16">
       <c r="A3" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
     </row>
     <row r="4" spans="1:16">
       <c r="A4" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
     </row>
     <row r="5" spans="1:16">
       <c r="A5" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
     </row>
     <row r="6" spans="1:16">
       <c r="A6" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
     </row>
     <row r="7" spans="1:16">
       <c r="A7" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
     </row>
     <row r="9" spans="1:16">
       <c r="A9" s="1" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="B9" s="1"/>
       <c r="C9" s="1"/>
@@ -2366,7 +2333,7 @@
         <v>1</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>38</v>
@@ -2396,20 +2363,20 @@
         <v>2</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="D11" s="1">
         <v>2</v>
       </c>
       <c r="E11" s="1"/>
       <c r="F11" s="1" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="H11" s="1"/>
       <c r="I11" s="1"/>
@@ -2426,20 +2393,20 @@
         <v>3</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="D12" s="1">
         <v>4</v>
       </c>
       <c r="E12" s="1"/>
       <c r="F12" s="1" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="H12" s="1"/>
       <c r="I12" s="1"/>
@@ -2456,20 +2423,20 @@
         <v>4</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D13" s="1">
         <v>5</v>
       </c>
       <c r="E13" s="1"/>
       <c r="F13" s="1" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="H13" s="1"/>
       <c r="I13" s="1"/>
@@ -2486,22 +2453,22 @@
         <v>5</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="D14" s="1">
         <v>3</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="H14" s="1"/>
       <c r="I14" s="1"/>
@@ -2518,10 +2485,10 @@
         <v>6</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D15" s="1">
         <v>6</v>
@@ -2544,17 +2511,17 @@
         <v>7</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D16" s="1">
         <v>7</v>
       </c>
       <c r="E16" s="1"/>
       <c r="F16" s="1" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="G16" s="1"/>
       <c r="H16" s="1"/>

--- a/hall/resources/sample/popUpConfig.xlsx
+++ b/hall/resources/sample/popUpConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255"/>
+    <workbookView windowWidth="27945" windowHeight="12975"/>
   </bookViews>
   <sheets>
     <sheet name="popUpConfig" sheetId="1" r:id="rId1"/>
@@ -108,12 +108,34 @@
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
+web专用</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="G1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
 界面名称_页签名称;
 注：页签名称为0时，表示打开指定界面即可；不要求精准</t>
         </r>
       </text>
     </comment>
-    <comment ref="N1" authorId="0">
+    <comment ref="O1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -135,7 +157,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="O1" authorId="0">
+    <comment ref="P1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -157,7 +179,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="P1" authorId="0">
+    <comment ref="Q1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -185,7 +207,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="106">
   <si>
     <t>序号ID</t>
   </si>
@@ -265,6 +287,9 @@
     <t>imgName</t>
   </si>
   <si>
+    <t>web_imgName</t>
+  </si>
+  <si>
     <t>functionUiName</t>
   </si>
   <si>
@@ -419,6 +444,12 @@
   </si>
   <si>
     <t>没有绑定手机号则弹出，绑定了就不弹出</t>
+  </si>
+  <si>
+    <t>%s/poptest.jpg</t>
+  </si>
+  <si>
+    <t>%s/web_poptest.jpg</t>
   </si>
   <si>
     <t>每日奖金(原月卡)：UIDailyBonus</t>
@@ -506,7 +537,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="29">
+  <fonts count="30">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -555,6 +586,13 @@
       <u/>
       <sz val="11"/>
       <color theme="0" tint="-0.35"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1047,138 +1085,138 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1246,6 +1284,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="6" applyNumberFormat="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="6" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" quotePrefix="1">
@@ -1575,34 +1616,35 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:Q15"/>
+  <dimension ref="A1:R15"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="7.25" style="5" customWidth="1"/>
     <col min="2" max="2" width="30.75" style="5" customWidth="1"/>
     <col min="3" max="3" width="35.5833333333333" style="5" customWidth="1"/>
     <col min="4" max="4" width="14.625" style="5" customWidth="1"/>
-    <col min="5" max="5" width="57.375" style="6" customWidth="1"/>
-    <col min="6" max="6" width="72.35" style="5" customWidth="1"/>
-    <col min="7" max="7" width="48.525" style="3" customWidth="1"/>
-    <col min="8" max="8" width="12.875" style="3" customWidth="1"/>
-    <col min="9" max="9" width="16.25" style="5" customWidth="1"/>
-    <col min="10" max="10" width="8.875" style="5" customWidth="1"/>
-    <col min="11" max="11" width="20.8833333333333" style="7" customWidth="1"/>
-    <col min="12" max="12" width="21.175" style="7" customWidth="1"/>
-    <col min="13" max="15" width="12.875" style="8" customWidth="1"/>
-    <col min="16" max="16" width="13.2333333333333" style="5" customWidth="1"/>
-    <col min="17" max="17" width="72.125" style="5" customWidth="1"/>
-    <col min="18" max="18" width="9.375" style="5"/>
-    <col min="19" max="19" width="19.875" style="5" customWidth="1"/>
-    <col min="20" max="20" width="13.75" style="5" customWidth="1"/>
-    <col min="21" max="21" width="9" style="5"/>
-    <col min="22" max="22" width="9.375" style="5"/>
-    <col min="23" max="23" width="23.25" style="5" customWidth="1"/>
-    <col min="24" max="16384" width="9" style="5"/>
+    <col min="5" max="5" width="17.125" style="6" customWidth="1"/>
+    <col min="6" max="6" width="22.5" style="6" customWidth="1"/>
+    <col min="7" max="7" width="72.35" style="5" customWidth="1"/>
+    <col min="8" max="8" width="48.525" style="3" customWidth="1"/>
+    <col min="9" max="9" width="12.875" style="3" customWidth="1"/>
+    <col min="10" max="10" width="16.25" style="5" customWidth="1"/>
+    <col min="11" max="11" width="8.875" style="5" customWidth="1"/>
+    <col min="12" max="12" width="20.8833333333333" style="7" customWidth="1"/>
+    <col min="13" max="13" width="21.175" style="7" customWidth="1"/>
+    <col min="14" max="16" width="12.875" style="8" customWidth="1"/>
+    <col min="17" max="17" width="13.2333333333333" style="5" customWidth="1"/>
+    <col min="18" max="18" width="72.125" style="5" customWidth="1"/>
+    <col min="19" max="19" width="9.375" style="5"/>
+    <col min="20" max="20" width="19.875" style="5" customWidth="1"/>
+    <col min="21" max="21" width="13.75" style="5" customWidth="1"/>
+    <col min="22" max="22" width="9" style="5"/>
+    <col min="23" max="23" width="9.375" style="5"/>
+    <col min="24" max="24" width="23.25" style="5" customWidth="1"/>
+    <col min="25" max="16384" width="9" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" s="2" customFormat="1" ht="15" spans="1:17">
+    <row r="1" s="2" customFormat="1" ht="15" spans="1:18">
       <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
@@ -1618,44 +1660,47 @@
       <c r="E1" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="9" t="s">
+      <c r="F1" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="11" t="s">
+      <c r="H1" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="12" t="s">
+      <c r="I1" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="9" t="s">
+      <c r="J1" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="9" t="s">
+      <c r="K1" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="13" t="s">
+      <c r="L1" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="13" t="s">
+      <c r="M1" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="14" t="s">
+      <c r="N1" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="14" t="s">
+      <c r="O1" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="14" t="s">
+      <c r="P1" s="14" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="14" t="s">
+      <c r="Q1" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="2" t="s">
+      <c r="R1" s="2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="2" s="2" customFormat="1" ht="15" spans="1:17">
+    <row r="2" s="2" customFormat="1" ht="15" spans="1:18">
       <c r="A2" s="9" t="s">
         <v>16</v>
       </c>
@@ -1670,40 +1715,43 @@
         <v>18</v>
       </c>
       <c r="F2" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="G2" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="G2" s="12" t="s">
+      <c r="H2" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="H2" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="I2" s="9" t="s">
+      <c r="I2" s="12" t="s">
         <v>20</v>
       </c>
       <c r="J2" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="K2" s="13" t="s">
-        <v>21</v>
+      <c r="K2" s="9" t="s">
+        <v>20</v>
       </c>
       <c r="L2" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="M2" s="14" t="s">
+      <c r="M2" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="N2" s="14" t="s">
         <v>16</v>
       </c>
-      <c r="N2" s="14" t="s">
+      <c r="O2" s="14" t="s">
         <v>21</v>
-      </c>
-      <c r="O2" s="14" t="s">
-        <v>16</v>
       </c>
       <c r="P2" s="14" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" s="2" customFormat="1" ht="15" spans="1:17">
+      <c r="Q2" s="14" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="3" s="2" customFormat="1" ht="15" spans="1:18">
       <c r="A3" s="9" t="s">
         <v>22</v>
       </c>
@@ -1717,28 +1765,28 @@
       <c r="E3" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="F3" s="9" t="s">
+      <c r="F3" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="G3" s="11" t="s">
+      <c r="G3" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="H3" s="12" t="s">
+      <c r="H3" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="I3" s="9" t="s">
+      <c r="I3" s="12" t="s">
         <v>29</v>
       </c>
       <c r="J3" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="K3" s="13" t="s">
+      <c r="K3" s="9" t="s">
         <v>31</v>
       </c>
       <c r="L3" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="M3" s="14" t="s">
+      <c r="M3" s="13" t="s">
         <v>33</v>
       </c>
       <c r="N3" s="14" t="s">
@@ -1750,186 +1798,191 @@
       <c r="P3" s="14" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="4" s="2" customFormat="1" ht="15" spans="1:17">
+      <c r="Q3" s="14" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="4" s="2" customFormat="1" ht="15" spans="1:18">
       <c r="A4" s="9"/>
       <c r="B4" s="9"/>
       <c r="C4" s="9"/>
       <c r="D4" s="9"/>
       <c r="E4" s="10"/>
-      <c r="F4" s="9"/>
-      <c r="G4" s="12"/>
+      <c r="F4" s="10"/>
+      <c r="G4" s="9"/>
       <c r="H4" s="12"/>
-      <c r="I4" s="9"/>
+      <c r="I4" s="12"/>
       <c r="J4" s="9"/>
-      <c r="K4" s="13"/>
+      <c r="K4" s="9"/>
       <c r="L4" s="13"/>
-      <c r="M4" s="14"/>
+      <c r="M4" s="13"/>
       <c r="N4" s="14"/>
       <c r="O4" s="14"/>
       <c r="P4" s="14"/>
-    </row>
-    <row r="5" s="3" customFormat="1" spans="1:17">
+      <c r="Q4" s="14"/>
+    </row>
+    <row r="5" s="3" customFormat="1" spans="1:18">
       <c r="A5" s="3">
         <v>1</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D5" s="3">
         <v>2</v>
       </c>
       <c r="E5" s="16"/>
-      <c r="F5" s="3" t="s">
-        <v>39</v>
-      </c>
+      <c r="F5" s="16"/>
       <c r="G5" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="H5" s="17" t="b">
+      <c r="H5" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="I5" s="17" t="b">
         <v>1</v>
       </c>
-      <c r="I5" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="J5" s="17" t="b">
+      <c r="J5" s="18" t="b">
+        <v>0</v>
+      </c>
+      <c r="K5" s="17" t="b">
         <v>1</v>
       </c>
-      <c r="K5" s="25" t="s">
-        <v>41</v>
-      </c>
-      <c r="L5" s="25" t="s">
+      <c r="L5" s="26" t="s">
         <v>42</v>
       </c>
-      <c r="M5" s="20">
+      <c r="M5" s="26" t="s">
+        <v>43</v>
+      </c>
+      <c r="N5" s="20">
         <v>99</v>
       </c>
-      <c r="N5" s="20"/>
       <c r="O5" s="20"/>
-      <c r="P5" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q5" s="3" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="6" s="3" customFormat="1" spans="1:17">
+      <c r="P5" s="20"/>
+      <c r="Q5" s="3">
+        <v>0</v>
+      </c>
+      <c r="R5" s="3" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="6" s="3" customFormat="1" spans="1:18">
       <c r="A6" s="3">
         <v>2</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D6" s="3">
         <v>3</v>
       </c>
       <c r="E6" s="16"/>
-      <c r="F6" s="3" t="s">
-        <v>46</v>
-      </c>
+      <c r="F6" s="16"/>
       <c r="G6" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="H6" s="17" t="b">
+      <c r="H6" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="I6" s="17" t="b">
         <v>1</v>
       </c>
-      <c r="I6" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="J6" s="17" t="b">
+      <c r="J6" s="18" t="b">
+        <v>0</v>
+      </c>
+      <c r="K6" s="17" t="b">
         <v>1</v>
       </c>
-      <c r="K6" s="25" t="s">
-        <v>41</v>
-      </c>
-      <c r="L6" s="25" t="s">
+      <c r="L6" s="26" t="s">
         <v>42</v>
       </c>
-      <c r="M6" s="20">
+      <c r="M6" s="26" t="s">
+        <v>43</v>
+      </c>
+      <c r="N6" s="20">
         <v>99</v>
       </c>
-      <c r="N6" s="20"/>
       <c r="O6" s="20"/>
-      <c r="P6" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q6" s="3" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="7" s="3" customFormat="1" spans="1:17">
+      <c r="P6" s="20"/>
+      <c r="Q6" s="3">
+        <v>0</v>
+      </c>
+      <c r="R6" s="3" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="7" s="3" customFormat="1" spans="1:18">
       <c r="A7" s="3">
         <v>3</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D7" s="3">
         <v>4</v>
       </c>
       <c r="E7" s="16"/>
-      <c r="F7" s="3" t="s">
-        <v>50</v>
-      </c>
+      <c r="F7" s="16"/>
       <c r="G7" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="H7" s="17" t="b">
+      <c r="H7" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="I7" s="17" t="b">
         <v>1</v>
       </c>
-      <c r="I7" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="J7" s="17" t="b">
+      <c r="J7" s="18" t="b">
+        <v>0</v>
+      </c>
+      <c r="K7" s="17" t="b">
         <v>1</v>
       </c>
-      <c r="K7" s="25" t="s">
-        <v>41</v>
-      </c>
-      <c r="L7" s="25" t="s">
+      <c r="L7" s="26" t="s">
         <v>42</v>
       </c>
-      <c r="M7" s="20">
+      <c r="M7" s="26" t="s">
+        <v>43</v>
+      </c>
+      <c r="N7" s="20">
         <v>99</v>
       </c>
-      <c r="N7" s="20"/>
       <c r="O7" s="20"/>
-      <c r="P7" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q7" s="3" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="8" s="4" customFormat="1" spans="1:17">
+      <c r="P7" s="20"/>
+      <c r="Q7" s="3">
+        <v>0</v>
+      </c>
+      <c r="R7" s="3" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="8" s="4" customFormat="1" spans="1:18">
       <c r="A8" s="4">
         <v>4</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D8" s="4"/>
       <c r="E8" s="21"/>
-      <c r="F8" s="4" t="s">
-        <v>54</v>
-      </c>
+      <c r="F8" s="21"/>
       <c r="G8" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="H8" s="18" t="b">
-        <v>0</v>
+      <c r="H8" s="4" t="s">
+        <v>56</v>
       </c>
       <c r="I8" s="18" t="b">
         <v>0</v>
@@ -1937,44 +1990,45 @@
       <c r="J8" s="18" t="b">
         <v>0</v>
       </c>
-      <c r="K8" s="26" t="s">
-        <v>41</v>
-      </c>
-      <c r="L8" s="26" t="s">
+      <c r="K8" s="18" t="b">
+        <v>0</v>
+      </c>
+      <c r="L8" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="M8" s="23">
+      <c r="M8" s="27" t="s">
+        <v>43</v>
+      </c>
+      <c r="N8" s="23">
         <v>3</v>
       </c>
-      <c r="N8" s="23"/>
       <c r="O8" s="23"/>
-      <c r="P8" s="4">
-        <v>0</v>
-      </c>
-      <c r="Q8" s="4" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="9" s="4" customFormat="1" spans="1:17">
+      <c r="P8" s="23"/>
+      <c r="Q8" s="4">
+        <v>0</v>
+      </c>
+      <c r="R8" s="4" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="9" s="4" customFormat="1" spans="1:18">
       <c r="A9" s="4">
         <v>5</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D9" s="4"/>
       <c r="E9" s="21"/>
-      <c r="F9" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="G9" s="18" t="s">
+      <c r="F9" s="21"/>
+      <c r="G9" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="H9" s="18" t="b">
-        <v>0</v>
+      <c r="H9" s="18" t="s">
+        <v>60</v>
       </c>
       <c r="I9" s="18" t="b">
         <v>0</v>
@@ -1982,85 +2036,87 @@
       <c r="J9" s="18" t="b">
         <v>0</v>
       </c>
-      <c r="K9" s="26" t="s">
-        <v>41</v>
-      </c>
-      <c r="L9" s="26" t="s">
+      <c r="K9" s="18" t="b">
+        <v>0</v>
+      </c>
+      <c r="L9" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="M9" s="23">
+      <c r="M9" s="27" t="s">
+        <v>43</v>
+      </c>
+      <c r="N9" s="23">
         <v>2</v>
       </c>
-      <c r="N9" s="23"/>
       <c r="O9" s="23"/>
-      <c r="P9" s="4">
-        <v>0</v>
-      </c>
-      <c r="Q9" s="4" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="10" s="4" customFormat="1" spans="1:17">
+      <c r="P9" s="23"/>
+      <c r="Q9" s="4">
+        <v>0</v>
+      </c>
+      <c r="R9" s="4" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="10" s="4" customFormat="1" spans="1:18">
       <c r="A10" s="4">
         <v>6</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D10" s="4"/>
       <c r="E10" s="21"/>
-      <c r="F10" s="4"/>
+      <c r="F10" s="21"/>
       <c r="G10" s="4"/>
-      <c r="H10" s="18" t="b">
-        <v>0</v>
-      </c>
+      <c r="H10" s="4"/>
       <c r="I10" s="18" t="b">
         <v>0</v>
       </c>
       <c r="J10" s="18" t="b">
         <v>0</v>
       </c>
-      <c r="K10" s="26" t="s">
-        <v>41</v>
-      </c>
-      <c r="L10" s="26" t="s">
-        <v>62</v>
-      </c>
-      <c r="M10" s="23">
+      <c r="K10" s="18" t="b">
+        <v>0</v>
+      </c>
+      <c r="L10" s="27" t="s">
+        <v>42</v>
+      </c>
+      <c r="M10" s="27" t="s">
+        <v>63</v>
+      </c>
+      <c r="N10" s="23">
         <v>1</v>
       </c>
-      <c r="N10" s="23"/>
       <c r="O10" s="23"/>
-      <c r="P10" s="4">
-        <v>0</v>
-      </c>
-      <c r="Q10" s="4" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="11" s="4" customFormat="1" spans="1:17">
+      <c r="P10" s="23"/>
+      <c r="Q10" s="4">
+        <v>0</v>
+      </c>
+      <c r="R10" s="4" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="11" s="4" customFormat="1" spans="1:18">
       <c r="A11" s="4">
         <v>7</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D11" s="4"/>
       <c r="E11" s="21"/>
-      <c r="F11" s="4" t="s">
-        <v>65</v>
-      </c>
+      <c r="F11" s="21"/>
       <c r="G11" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="H11" s="18" t="b">
-        <v>0</v>
+      <c r="H11" s="4" t="s">
+        <v>67</v>
       </c>
       <c r="I11" s="18" t="b">
         <v>0</v>
@@ -2068,193 +2124,206 @@
       <c r="J11" s="18" t="b">
         <v>0</v>
       </c>
-      <c r="K11" s="26" t="s">
-        <v>67</v>
-      </c>
-      <c r="L11" s="26" t="s">
+      <c r="K11" s="18" t="b">
+        <v>0</v>
+      </c>
+      <c r="L11" s="27" t="s">
         <v>68</v>
       </c>
-      <c r="M11" s="23">
+      <c r="M11" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="N11" s="23">
         <v>99</v>
       </c>
-      <c r="N11" s="23"/>
       <c r="O11" s="23"/>
-      <c r="P11" s="4">
+      <c r="P11" s="23"/>
+      <c r="Q11" s="4">
         <v>1</v>
       </c>
-      <c r="Q11" s="4" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="12" s="4" customFormat="1" spans="1:17">
+      <c r="R11" s="4" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="12" s="4" customFormat="1" spans="1:18">
       <c r="A12" s="4">
         <v>8</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D12" s="4"/>
       <c r="E12" s="21"/>
-      <c r="F12" s="4"/>
+      <c r="F12" s="21"/>
       <c r="G12" s="4"/>
-      <c r="H12" s="18" t="b">
-        <v>0</v>
-      </c>
+      <c r="H12" s="4"/>
       <c r="I12" s="18" t="b">
         <v>0</v>
       </c>
       <c r="J12" s="18" t="b">
         <v>0</v>
       </c>
-      <c r="K12" s="26" t="s">
-        <v>41</v>
-      </c>
-      <c r="L12" s="26" t="s">
+      <c r="K12" s="18" t="b">
+        <v>0</v>
+      </c>
+      <c r="L12" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="M12" s="23">
+      <c r="M12" s="27" t="s">
+        <v>43</v>
+      </c>
+      <c r="N12" s="23">
         <v>1</v>
       </c>
-      <c r="N12" s="23"/>
       <c r="O12" s="23"/>
-      <c r="P12" s="4">
-        <v>0</v>
-      </c>
-      <c r="Q12" s="4" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="13" s="4" customFormat="1" spans="1:17">
+      <c r="P12" s="23"/>
+      <c r="Q12" s="4">
+        <v>0</v>
+      </c>
+      <c r="R12" s="4" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="13" s="4" customFormat="1" spans="1:18">
       <c r="A13" s="4">
         <v>9</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D13" s="4"/>
       <c r="E13" s="21"/>
       <c r="F13" s="21"/>
-      <c r="G13" s="4"/>
-      <c r="H13" s="18" t="b">
-        <v>0</v>
-      </c>
+      <c r="G13" s="21"/>
+      <c r="H13" s="4"/>
       <c r="I13" s="18" t="b">
         <v>0</v>
       </c>
       <c r="J13" s="18" t="b">
         <v>0</v>
       </c>
-      <c r="K13" s="26" t="s">
-        <v>67</v>
-      </c>
-      <c r="L13" s="26" t="s">
-        <v>73</v>
-      </c>
-      <c r="M13" s="23">
+      <c r="K13" s="18" t="b">
+        <v>0</v>
+      </c>
+      <c r="L13" s="27" t="s">
+        <v>68</v>
+      </c>
+      <c r="M13" s="27" t="s">
+        <v>74</v>
+      </c>
+      <c r="N13" s="23">
         <v>99</v>
       </c>
-      <c r="N13" s="24"/>
-      <c r="O13" s="21"/>
-      <c r="P13" s="4">
-        <v>0</v>
-      </c>
-      <c r="Q13" s="4" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="14" s="3" customFormat="1" spans="1:17">
+      <c r="O13" s="24"/>
+      <c r="P13" s="21"/>
+      <c r="Q13" s="4">
+        <v>0</v>
+      </c>
+      <c r="R13" s="4" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="14" s="3" customFormat="1" spans="1:18">
       <c r="A14" s="3">
         <v>10</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D14" s="3">
         <v>1</v>
       </c>
       <c r="E14" s="16"/>
-      <c r="F14" s="3"/>
-      <c r="H14" s="17" t="b">
+      <c r="F14" s="16"/>
+      <c r="G14" s="3"/>
+      <c r="I14" s="17" t="b">
         <v>1</v>
       </c>
-      <c r="I14" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="J14" s="17" t="b">
+      <c r="J14" s="18" t="b">
+        <v>0</v>
+      </c>
+      <c r="K14" s="17" t="b">
         <v>1</v>
       </c>
-      <c r="K14" s="25" t="s">
-        <v>67</v>
-      </c>
-      <c r="L14" s="25" t="s">
+      <c r="L14" s="26" t="s">
         <v>68</v>
       </c>
-      <c r="M14" s="20">
+      <c r="M14" s="26" t="s">
+        <v>69</v>
+      </c>
+      <c r="N14" s="20">
         <v>99</v>
       </c>
-      <c r="N14" s="20"/>
       <c r="O14" s="20"/>
-      <c r="P14" s="4">
-        <v>0</v>
-      </c>
-      <c r="Q14" s="3" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="15" s="4" customFormat="1" spans="1:17">
-      <c r="A15" s="4">
+      <c r="P14" s="20"/>
+      <c r="Q14" s="4">
+        <v>0</v>
+      </c>
+      <c r="R14" s="3" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="15" s="3" customFormat="1" spans="1:18">
+      <c r="A15" s="3">
         <v>11</v>
       </c>
-      <c r="B15" s="4" t="s">
-        <v>71</v>
-      </c>
-      <c r="C15" s="4" t="s">
+      <c r="B15" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="D15" s="4"/>
-      <c r="E15" s="21"/>
-      <c r="F15" s="21"/>
-      <c r="H15" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="I15" s="18" t="b">
-        <v>0</v>
+      <c r="C15" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="D15" s="3">
+        <v>5</v>
+      </c>
+      <c r="E15" s="16" t="s">
+        <v>79</v>
+      </c>
+      <c r="F15" s="16" t="s">
+        <v>80</v>
+      </c>
+      <c r="G15" s="16"/>
+      <c r="I15" s="17" t="b">
+        <v>1</v>
       </c>
       <c r="J15" s="18" t="b">
         <v>0</v>
       </c>
-      <c r="K15" s="26" t="s">
-        <v>67</v>
+      <c r="K15" s="17" t="b">
+        <v>1</v>
       </c>
       <c r="L15" s="26" t="s">
         <v>68</v>
       </c>
-      <c r="M15" s="23">
+      <c r="M15" s="26" t="s">
+        <v>69</v>
+      </c>
+      <c r="N15" s="20">
         <v>99</v>
       </c>
-      <c r="N15" s="24"/>
-      <c r="O15" s="21"/>
-      <c r="P15" s="4">
-        <v>0</v>
-      </c>
-      <c r="Q15" s="4" t="s">
-        <v>74</v>
+      <c r="O15" s="25"/>
+      <c r="P15" s="16"/>
+      <c r="Q15" s="3">
+        <v>0</v>
+      </c>
+      <c r="R15" s="3" t="s">
+        <v>75</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="O13">
+  <conditionalFormatting sqref="P13">
     <cfRule type="duplicateValues" dxfId="0" priority="2"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O15">
+  <conditionalFormatting sqref="P15">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2275,42 +2344,42 @@
   <sheetData>
     <row r="1" spans="1:16">
       <c r="A1" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
     </row>
     <row r="2" spans="1:16">
       <c r="A2" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
     </row>
     <row r="3" spans="1:16">
       <c r="A3" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
     </row>
     <row r="4" spans="1:16">
       <c r="A4" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
     </row>
     <row r="5" spans="1:16">
       <c r="A5" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
     </row>
     <row r="6" spans="1:16">
       <c r="A6" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
     </row>
     <row r="7" spans="1:16">
       <c r="A7" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
     </row>
     <row r="9" spans="1:16">
       <c r="A9" s="1" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="B9" s="1"/>
       <c r="C9" s="1"/>
@@ -2333,20 +2402,20 @@
         <v>1</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D10" s="1">
         <v>1</v>
       </c>
       <c r="E10" s="1"/>
       <c r="F10" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H10" s="1"/>
       <c r="I10" s="1"/>
@@ -2363,20 +2432,20 @@
         <v>2</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="D11" s="1">
         <v>2</v>
       </c>
       <c r="E11" s="1"/>
       <c r="F11" s="1" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="H11" s="1"/>
       <c r="I11" s="1"/>
@@ -2393,20 +2462,20 @@
         <v>3</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="D12" s="1">
         <v>4</v>
       </c>
       <c r="E12" s="1"/>
       <c r="F12" s="1" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="H12" s="1"/>
       <c r="I12" s="1"/>
@@ -2423,20 +2492,20 @@
         <v>4</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D13" s="1">
         <v>5</v>
       </c>
       <c r="E13" s="1"/>
       <c r="F13" s="1" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="H13" s="1"/>
       <c r="I13" s="1"/>
@@ -2453,22 +2522,22 @@
         <v>5</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="D14" s="1">
         <v>3</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="H14" s="1"/>
       <c r="I14" s="1"/>
@@ -2485,10 +2554,10 @@
         <v>6</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D15" s="1">
         <v>6</v>
@@ -2511,17 +2580,17 @@
         <v>7</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D16" s="1">
         <v>7</v>
       </c>
       <c r="E16" s="1"/>
       <c r="F16" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G16" s="1"/>
       <c r="H16" s="1"/>

--- a/hall/resources/sample/popUpConfig.xlsx
+++ b/hall/resources/sample/popUpConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12975"/>
+    <workbookView windowWidth="27945" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="popUpConfig" sheetId="1" r:id="rId1"/>
@@ -207,7 +207,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="104">
   <si>
     <t>序号ID</t>
   </si>
@@ -444,12 +444,6 @@
   </si>
   <si>
     <t>没有绑定手机号则弹出，绑定了就不弹出</t>
-  </si>
-  <si>
-    <t>%s/poptest.jpg</t>
-  </si>
-  <si>
-    <t>%s/web_poptest.jpg</t>
   </si>
   <si>
     <t>每日奖金(原月卡)：UIDailyBonus</t>
@@ -537,7 +531,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="30">
+  <fonts count="29">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -554,6 +548,7 @@
     </font>
     <font>
       <sz val="11"/>
+      <color theme="1"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
@@ -565,7 +560,6 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
@@ -586,13 +580,6 @@
       <u/>
       <sz val="11"/>
       <color theme="0" tint="-0.35"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1085,138 +1072,138 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1232,16 +1219,16 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1">
@@ -1263,17 +1250,8 @@
     <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1284,9 +1262,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="6" applyNumberFormat="1" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="6" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" quotePrefix="1">
@@ -1619,29 +1594,29 @@
   <dimension ref="A1:R15"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
-    <col min="1" max="1" width="7.25" style="5" customWidth="1"/>
-    <col min="2" max="2" width="30.75" style="5" customWidth="1"/>
-    <col min="3" max="3" width="35.5833333333333" style="5" customWidth="1"/>
-    <col min="4" max="4" width="14.625" style="5" customWidth="1"/>
-    <col min="5" max="5" width="17.125" style="6" customWidth="1"/>
-    <col min="6" max="6" width="22.5" style="6" customWidth="1"/>
-    <col min="7" max="7" width="72.35" style="5" customWidth="1"/>
-    <col min="8" max="8" width="48.525" style="3" customWidth="1"/>
-    <col min="9" max="9" width="12.875" style="3" customWidth="1"/>
-    <col min="10" max="10" width="16.25" style="5" customWidth="1"/>
-    <col min="11" max="11" width="8.875" style="5" customWidth="1"/>
+    <col min="1" max="1" width="7.25" style="3" customWidth="1"/>
+    <col min="2" max="2" width="30.75" style="3" customWidth="1"/>
+    <col min="3" max="3" width="35.5833333333333" style="3" customWidth="1"/>
+    <col min="4" max="4" width="14.625" style="3" customWidth="1"/>
+    <col min="5" max="5" width="17.125" style="5" customWidth="1"/>
+    <col min="6" max="6" width="22.5" style="5" customWidth="1"/>
+    <col min="7" max="7" width="72.35" style="3" customWidth="1"/>
+    <col min="8" max="8" width="48.525" style="6" customWidth="1"/>
+    <col min="9" max="9" width="12.875" style="6" customWidth="1"/>
+    <col min="10" max="10" width="16.25" style="4" customWidth="1"/>
+    <col min="11" max="11" width="8.875" style="3" customWidth="1"/>
     <col min="12" max="12" width="20.8833333333333" style="7" customWidth="1"/>
     <col min="13" max="13" width="21.175" style="7" customWidth="1"/>
     <col min="14" max="16" width="12.875" style="8" customWidth="1"/>
-    <col min="17" max="17" width="13.2333333333333" style="5" customWidth="1"/>
-    <col min="18" max="18" width="72.125" style="5" customWidth="1"/>
-    <col min="19" max="19" width="9.375" style="5"/>
-    <col min="20" max="20" width="19.875" style="5" customWidth="1"/>
-    <col min="21" max="21" width="13.75" style="5" customWidth="1"/>
-    <col min="22" max="22" width="9" style="5"/>
-    <col min="23" max="23" width="9.375" style="5"/>
-    <col min="24" max="24" width="23.25" style="5" customWidth="1"/>
-    <col min="25" max="16384" width="9" style="5"/>
+    <col min="17" max="17" width="13.2333333333333" style="3" customWidth="1"/>
+    <col min="18" max="18" width="72.125" style="3" customWidth="1"/>
+    <col min="19" max="19" width="9.375" style="3"/>
+    <col min="20" max="20" width="19.875" style="3" customWidth="1"/>
+    <col min="21" max="21" width="13.75" style="3" customWidth="1"/>
+    <col min="22" max="22" width="9" style="3"/>
+    <col min="23" max="23" width="9.375" style="3"/>
+    <col min="24" max="24" width="23.25" style="3" customWidth="1"/>
+    <col min="25" max="16384" width="9" style="3"/>
   </cols>
   <sheetData>
     <row r="1" s="2" customFormat="1" ht="15" spans="1:18">
@@ -1672,7 +1647,7 @@
       <c r="I1" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="J1" s="9" t="s">
+      <c r="J1" s="12" t="s">
         <v>8</v>
       </c>
       <c r="K1" s="9" t="s">
@@ -1726,7 +1701,7 @@
       <c r="I2" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="J2" s="9" t="s">
+      <c r="J2" s="12" t="s">
         <v>20</v>
       </c>
       <c r="K2" s="9" t="s">
@@ -1777,7 +1752,7 @@
       <c r="I3" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="J3" s="9" t="s">
+      <c r="J3" s="12" t="s">
         <v>30</v>
       </c>
       <c r="K3" s="9" t="s">
@@ -1812,7 +1787,7 @@
       <c r="G4" s="9"/>
       <c r="H4" s="12"/>
       <c r="I4" s="12"/>
-      <c r="J4" s="9"/>
+      <c r="J4" s="12"/>
       <c r="K4" s="9"/>
       <c r="L4" s="13"/>
       <c r="M4" s="13"/>
@@ -1834,34 +1809,34 @@
       <c r="D5" s="3">
         <v>2</v>
       </c>
-      <c r="E5" s="16"/>
-      <c r="F5" s="16"/>
+      <c r="E5" s="5"/>
+      <c r="F5" s="5"/>
       <c r="G5" s="3" t="s">
         <v>40</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="I5" s="17" t="b">
+      <c r="I5" s="16" t="b">
         <v>1</v>
       </c>
-      <c r="J5" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="K5" s="17" t="b">
+      <c r="J5" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="K5" s="16" t="b">
         <v>1</v>
       </c>
-      <c r="L5" s="26" t="s">
+      <c r="L5" s="22" t="s">
         <v>42</v>
       </c>
-      <c r="M5" s="26" t="s">
+      <c r="M5" s="22" t="s">
         <v>43</v>
       </c>
-      <c r="N5" s="20">
+      <c r="N5" s="8">
         <v>99</v>
       </c>
-      <c r="O5" s="20"/>
-      <c r="P5" s="20"/>
+      <c r="O5" s="8"/>
+      <c r="P5" s="8"/>
       <c r="Q5" s="3">
         <v>0</v>
       </c>
@@ -1882,34 +1857,34 @@
       <c r="D6" s="3">
         <v>3</v>
       </c>
-      <c r="E6" s="16"/>
-      <c r="F6" s="16"/>
+      <c r="E6" s="5"/>
+      <c r="F6" s="5"/>
       <c r="G6" s="3" t="s">
         <v>47</v>
       </c>
       <c r="H6" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="I6" s="17" t="b">
+      <c r="I6" s="16" t="b">
         <v>1</v>
       </c>
-      <c r="J6" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="K6" s="17" t="b">
+      <c r="J6" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="K6" s="16" t="b">
         <v>1</v>
       </c>
-      <c r="L6" s="26" t="s">
+      <c r="L6" s="22" t="s">
         <v>42</v>
       </c>
-      <c r="M6" s="26" t="s">
+      <c r="M6" s="22" t="s">
         <v>43</v>
       </c>
-      <c r="N6" s="20">
+      <c r="N6" s="8">
         <v>99</v>
       </c>
-      <c r="O6" s="20"/>
-      <c r="P6" s="20"/>
+      <c r="O6" s="8"/>
+      <c r="P6" s="8"/>
       <c r="Q6" s="3">
         <v>0</v>
       </c>
@@ -1930,34 +1905,34 @@
       <c r="D7" s="3">
         <v>4</v>
       </c>
-      <c r="E7" s="16"/>
-      <c r="F7" s="16"/>
+      <c r="E7" s="5"/>
+      <c r="F7" s="5"/>
       <c r="G7" s="3" t="s">
         <v>51</v>
       </c>
       <c r="H7" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="I7" s="17" t="b">
+      <c r="I7" s="16" t="b">
         <v>1</v>
       </c>
-      <c r="J7" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="K7" s="17" t="b">
+      <c r="J7" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="K7" s="16" t="b">
         <v>1</v>
       </c>
-      <c r="L7" s="26" t="s">
+      <c r="L7" s="22" t="s">
         <v>42</v>
       </c>
-      <c r="M7" s="26" t="s">
+      <c r="M7" s="22" t="s">
         <v>43</v>
       </c>
-      <c r="N7" s="20">
+      <c r="N7" s="8">
         <v>99</v>
       </c>
-      <c r="O7" s="20"/>
-      <c r="P7" s="20"/>
+      <c r="O7" s="8"/>
+      <c r="P7" s="8"/>
       <c r="Q7" s="3">
         <v>0</v>
       </c>
@@ -1976,34 +1951,34 @@
         <v>54</v>
       </c>
       <c r="D8" s="4"/>
-      <c r="E8" s="21"/>
-      <c r="F8" s="21"/>
+      <c r="E8" s="18"/>
+      <c r="F8" s="18"/>
       <c r="G8" s="4" t="s">
         <v>55</v>
       </c>
       <c r="H8" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="I8" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="J8" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="K8" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="L8" s="27" t="s">
+      <c r="I8" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="J8" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="K8" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="L8" s="23" t="s">
         <v>42</v>
       </c>
-      <c r="M8" s="27" t="s">
+      <c r="M8" s="23" t="s">
         <v>43</v>
       </c>
-      <c r="N8" s="23">
+      <c r="N8" s="20">
         <v>3</v>
       </c>
-      <c r="O8" s="23"/>
-      <c r="P8" s="23"/>
+      <c r="O8" s="20"/>
+      <c r="P8" s="20"/>
       <c r="Q8" s="4">
         <v>0</v>
       </c>
@@ -2022,34 +1997,34 @@
         <v>58</v>
       </c>
       <c r="D9" s="4"/>
-      <c r="E9" s="21"/>
-      <c r="F9" s="21"/>
+      <c r="E9" s="18"/>
+      <c r="F9" s="18"/>
       <c r="G9" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="H9" s="18" t="s">
+      <c r="H9" s="17" t="s">
         <v>60</v>
       </c>
-      <c r="I9" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="J9" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="K9" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="L9" s="27" t="s">
+      <c r="I9" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="J9" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="K9" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="L9" s="23" t="s">
         <v>42</v>
       </c>
-      <c r="M9" s="27" t="s">
+      <c r="M9" s="23" t="s">
         <v>43</v>
       </c>
-      <c r="N9" s="23">
+      <c r="N9" s="20">
         <v>2</v>
       </c>
-      <c r="O9" s="23"/>
-      <c r="P9" s="23"/>
+      <c r="O9" s="20"/>
+      <c r="P9" s="20"/>
       <c r="Q9" s="4">
         <v>0</v>
       </c>
@@ -2068,30 +2043,30 @@
         <v>62</v>
       </c>
       <c r="D10" s="4"/>
-      <c r="E10" s="21"/>
-      <c r="F10" s="21"/>
+      <c r="E10" s="18"/>
+      <c r="F10" s="18"/>
       <c r="G10" s="4"/>
       <c r="H10" s="4"/>
-      <c r="I10" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="J10" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="K10" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="L10" s="27" t="s">
+      <c r="I10" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="J10" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="K10" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="L10" s="23" t="s">
         <v>42</v>
       </c>
-      <c r="M10" s="27" t="s">
+      <c r="M10" s="23" t="s">
         <v>63</v>
       </c>
-      <c r="N10" s="23">
+      <c r="N10" s="20">
         <v>1</v>
       </c>
-      <c r="O10" s="23"/>
-      <c r="P10" s="23"/>
+      <c r="O10" s="20"/>
+      <c r="P10" s="20"/>
       <c r="Q10" s="4">
         <v>0</v>
       </c>
@@ -2110,34 +2085,34 @@
         <v>65</v>
       </c>
       <c r="D11" s="4"/>
-      <c r="E11" s="21"/>
-      <c r="F11" s="21"/>
+      <c r="E11" s="18"/>
+      <c r="F11" s="18"/>
       <c r="G11" s="4" t="s">
         <v>66</v>
       </c>
       <c r="H11" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="I11" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="J11" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="K11" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="L11" s="27" t="s">
+      <c r="I11" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="J11" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="K11" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="L11" s="23" t="s">
         <v>68</v>
       </c>
-      <c r="M11" s="27" t="s">
+      <c r="M11" s="23" t="s">
         <v>69</v>
       </c>
-      <c r="N11" s="23">
+      <c r="N11" s="20">
         <v>99</v>
       </c>
-      <c r="O11" s="23"/>
-      <c r="P11" s="23"/>
+      <c r="O11" s="20"/>
+      <c r="P11" s="20"/>
       <c r="Q11" s="4">
         <v>1</v>
       </c>
@@ -2156,30 +2131,30 @@
         <v>71</v>
       </c>
       <c r="D12" s="4"/>
-      <c r="E12" s="21"/>
-      <c r="F12" s="21"/>
+      <c r="E12" s="18"/>
+      <c r="F12" s="18"/>
       <c r="G12" s="4"/>
       <c r="H12" s="4"/>
-      <c r="I12" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="J12" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="K12" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="L12" s="27" t="s">
+      <c r="I12" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="J12" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="K12" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="L12" s="23" t="s">
         <v>42</v>
       </c>
-      <c r="M12" s="27" t="s">
+      <c r="M12" s="23" t="s">
         <v>43</v>
       </c>
-      <c r="N12" s="23">
+      <c r="N12" s="20">
         <v>1</v>
       </c>
-      <c r="O12" s="23"/>
-      <c r="P12" s="23"/>
+      <c r="O12" s="20"/>
+      <c r="P12" s="20"/>
       <c r="Q12" s="4">
         <v>0</v>
       </c>
@@ -2198,30 +2173,30 @@
         <v>73</v>
       </c>
       <c r="D13" s="4"/>
-      <c r="E13" s="21"/>
-      <c r="F13" s="21"/>
-      <c r="G13" s="21"/>
+      <c r="E13" s="18"/>
+      <c r="F13" s="18"/>
+      <c r="G13" s="18"/>
       <c r="H13" s="4"/>
-      <c r="I13" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="J13" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="K13" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="L13" s="27" t="s">
+      <c r="I13" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="J13" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="K13" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="L13" s="23" t="s">
         <v>68</v>
       </c>
-      <c r="M13" s="27" t="s">
+      <c r="M13" s="23" t="s">
         <v>74</v>
       </c>
-      <c r="N13" s="23">
+      <c r="N13" s="20">
         <v>99</v>
       </c>
-      <c r="O13" s="24"/>
-      <c r="P13" s="21"/>
+      <c r="O13" s="21"/>
+      <c r="P13" s="18"/>
       <c r="Q13" s="4">
         <v>0</v>
       </c>
@@ -2242,80 +2217,74 @@
       <c r="D14" s="3">
         <v>1</v>
       </c>
-      <c r="E14" s="16"/>
-      <c r="F14" s="16"/>
+      <c r="E14" s="5"/>
+      <c r="F14" s="5"/>
       <c r="G14" s="3"/>
-      <c r="I14" s="17" t="b">
+      <c r="I14" s="16" t="b">
         <v>1</v>
       </c>
-      <c r="J14" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="K14" s="17" t="b">
+      <c r="J14" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="K14" s="16" t="b">
         <v>1</v>
       </c>
-      <c r="L14" s="26" t="s">
+      <c r="L14" s="22" t="s">
         <v>68</v>
       </c>
-      <c r="M14" s="26" t="s">
+      <c r="M14" s="22" t="s">
         <v>69</v>
       </c>
-      <c r="N14" s="20">
+      <c r="N14" s="8">
         <v>99</v>
       </c>
-      <c r="O14" s="20"/>
-      <c r="P14" s="20"/>
-      <c r="Q14" s="4">
+      <c r="O14" s="8"/>
+      <c r="P14" s="8"/>
+      <c r="Q14" s="3">
         <v>0</v>
       </c>
       <c r="R14" s="3" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="15" s="3" customFormat="1" spans="1:18">
-      <c r="A15" s="3">
+    <row r="15" s="4" customFormat="1" spans="1:18">
+      <c r="A15" s="4">
         <v>11</v>
       </c>
-      <c r="B15" s="3" t="s">
+      <c r="B15" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="C15" s="3" t="s">
+      <c r="C15" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="D15" s="3">
-        <v>5</v>
-      </c>
-      <c r="E15" s="16" t="s">
-        <v>79</v>
-      </c>
-      <c r="F15" s="16" t="s">
-        <v>80</v>
-      </c>
-      <c r="G15" s="16"/>
+      <c r="D15" s="4"/>
+      <c r="E15" s="18"/>
+      <c r="F15" s="18"/>
+      <c r="G15" s="18"/>
       <c r="I15" s="17" t="b">
-        <v>1</v>
-      </c>
-      <c r="J15" s="18" t="b">
+        <v>0</v>
+      </c>
+      <c r="J15" s="17" t="b">
         <v>0</v>
       </c>
       <c r="K15" s="17" t="b">
-        <v>1</v>
-      </c>
-      <c r="L15" s="26" t="s">
+        <v>0</v>
+      </c>
+      <c r="L15" s="23" t="s">
         <v>68</v>
       </c>
-      <c r="M15" s="26" t="s">
+      <c r="M15" s="23" t="s">
         <v>69</v>
       </c>
       <c r="N15" s="20">
         <v>99</v>
       </c>
-      <c r="O15" s="25"/>
-      <c r="P15" s="16"/>
-      <c r="Q15" s="3">
-        <v>0</v>
-      </c>
-      <c r="R15" s="3" t="s">
+      <c r="O15" s="21"/>
+      <c r="P15" s="18"/>
+      <c r="Q15" s="4">
+        <v>0</v>
+      </c>
+      <c r="R15" s="4" t="s">
         <v>75</v>
       </c>
     </row>
@@ -2344,42 +2313,42 @@
   <sheetData>
     <row r="1" spans="1:16">
       <c r="A1" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="2" spans="1:16">
       <c r="A2" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="3" spans="1:16">
       <c r="A3" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="4" spans="1:16">
       <c r="A4" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
     </row>
     <row r="5" spans="1:16">
       <c r="A5" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
     <row r="6" spans="1:16">
       <c r="A6" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
     </row>
     <row r="7" spans="1:16">
       <c r="A7" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="9" spans="1:16">
       <c r="A9" s="1" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B9" s="1"/>
       <c r="C9" s="1"/>
@@ -2402,7 +2371,7 @@
         <v>1</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>39</v>
@@ -2432,20 +2401,20 @@
         <v>2</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="D11" s="1">
         <v>2</v>
       </c>
       <c r="E11" s="1"/>
       <c r="F11" s="1" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="H11" s="1"/>
       <c r="I11" s="1"/>
@@ -2462,20 +2431,20 @@
         <v>3</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="D12" s="1">
         <v>4</v>
       </c>
       <c r="E12" s="1"/>
       <c r="F12" s="1" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="H12" s="1"/>
       <c r="I12" s="1"/>
@@ -2492,7 +2461,7 @@
         <v>4</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>54</v>
@@ -2502,10 +2471,10 @@
       </c>
       <c r="E13" s="1"/>
       <c r="F13" s="1" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="H13" s="1"/>
       <c r="I13" s="1"/>
@@ -2522,22 +2491,22 @@
         <v>5</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="D14" s="1">
         <v>3</v>
       </c>
       <c r="E14" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="G14" s="1" t="s">
         <v>103</v>
-      </c>
-      <c r="F14" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="G14" s="1" t="s">
-        <v>105</v>
       </c>
       <c r="H14" s="1"/>
       <c r="I14" s="1"/>

--- a/hall/resources/sample/popUpConfig.xlsx
+++ b/hall/resources/sample/popUpConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255"/>
+    <workbookView windowWidth="27945" windowHeight="11925"/>
   </bookViews>
   <sheets>
     <sheet name="popUpConfig" sheetId="1" r:id="rId1"/>
@@ -27,165 +27,8 @@
 </workbook>
 </file>
 
-<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <authors>
-    <author>Administrator</author>
-  </authors>
-  <commentList>
-    <comment ref="B1" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t>Administrator:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">
-1. 活动：ActivityConfig.xlsx  读取该表中的活动&lt;type&gt;字段值
-2. 功能：GameFunction.xlsx 读取该表中的&lt;ID&gt;字段值
-3. 游戏ID：warehouse.xlsx 读取该表中的&lt;gameID&gt;字段值
-4. 是功能同时也是活动  配置warehouse.xlsx 读取该表中的&lt;ID&gt;字段值
-描述：配置多个功能弹窗时，随机一个弹出；仅配置一个 则必弹；
-5. 手机绑定弹窗
-99.纯弹窗&amp;外部链接跳转URL
-参数例子：
-   1_11       //类型ID_对应功能ID
-或 1_11;2_9  // 类型ID1_对应功能ID1;类型ID2_对应功能ID2</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="C1" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t>Administrator:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">
-1：手机端
-2：webGL端</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="F1" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t>Administrator:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">
-宣传图名称_页签名称; 
-页签名称通常为0，除非宣传图上有页签功能
-注：页签名称为0时，表示打开指定界面即可；不要求精准
-弹窗宣传图资源  是从资源服实时下载的；后台没有配置表
-tanchuang_res/资源名称.png(或gif)</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="G1" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t>Administrator:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">
-界面名称_页签名称;
-注：页签名称为0时，表示打开指定界面即可；不要求精准</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="O1" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t>Administrator:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">
-URL仅匹配 类型为 “ 99” 的</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="P1" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t>Administrator:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">
-有值显示帮助文本按钮，反之  不显示帮助按钮</t>
-        </r>
-      </text>
-    </comment>
-  </commentList>
-</comments>
-</file>
-
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="104">
   <si>
     <t>序号ID</t>
   </si>
@@ -193,9 +36,6 @@
     <t>弹窗类型值</t>
   </si>
   <si>
-    <t>弹窗对应平台</t>
-  </si>
-  <si>
     <t>#备注</t>
   </si>
   <si>
@@ -235,6 +75,9 @@
     <t>帮助文本</t>
   </si>
   <si>
+    <t>弹窗提示语</t>
+  </si>
+  <si>
     <t>int</t>
   </si>
   <si>
@@ -265,6 +108,9 @@
     <t>imgName</t>
   </si>
   <si>
+    <t>web_imgName</t>
+  </si>
+  <si>
     <t>functionUiName</t>
   </si>
   <si>
@@ -295,6 +141,9 @@
     <t>help</t>
   </si>
   <si>
+    <t>Prompt</t>
+  </si>
+  <si>
     <t>4_106</t>
   </si>
   <si>
@@ -322,9 +171,6 @@
     <t>每日奖金;摇钱树;签到奖励</t>
   </si>
   <si>
-    <t>tanchuang_res/%s/tc_mrjj_1.png;0;0</t>
-  </si>
-  <si>
     <t>UIDailyBonus_0;UICashCow_0;UISignIn_0</t>
   </si>
   <si>
@@ -361,9 +207,6 @@
     <t>商城;成长基金</t>
   </si>
   <si>
-    <t>tanchuang_res/%s/tc_sc_1.png;tanchuang_res/%s/tc_czjj_1.png</t>
-  </si>
-  <si>
     <t>UIMall_0;UIGoldFund_0</t>
   </si>
   <si>
@@ -391,6 +234,9 @@
     <t>PlatformHall/UINotice/MVCHead</t>
   </si>
   <si>
+    <t>2025/12/1 0:00:00</t>
+  </si>
+  <si>
     <t>19_121</t>
   </si>
   <si>
@@ -401,12 +247,6 @@
   </si>
   <si>
     <t>纯弹窗&amp;外部链接</t>
-  </si>
-  <si>
-    <t>tanchuang_res/%s/tanchuang-test1.png</t>
-  </si>
-  <si>
-    <t>2025/12/1 0:00:00</t>
   </si>
   <si>
     <t>2025/12/31 23:59:59</t>
@@ -512,7 +352,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="29">
+  <fonts count="27">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -547,13 +387,13 @@
     <font>
       <b/>
       <sz val="11"/>
+      <color indexed="8"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
-      <color indexed="8"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
@@ -708,17 +548,6 @@
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <charset val="134"/>
     </font>
   </fonts>
   <fills count="35">
@@ -1184,7 +1013,7 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1215,25 +1044,22 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1587,15 +1413,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:Q14"/>
+  <dimension ref="A1:R15"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="7.25" style="5" customWidth="1"/>
     <col min="2" max="2" width="30.75" style="5" customWidth="1"/>
-    <col min="3" max="3" width="21.7583333333333" style="5" customWidth="1"/>
-    <col min="4" max="4" width="35.5833333333333" style="5" customWidth="1"/>
-    <col min="5" max="5" width="14.625" style="5" customWidth="1"/>
-    <col min="6" max="6" width="57.375" style="6" customWidth="1"/>
+    <col min="3" max="3" width="35.5833333333333" style="5" customWidth="1"/>
+    <col min="4" max="4" width="14.625" style="5" customWidth="1"/>
+    <col min="5" max="6" width="57.375" style="6" customWidth="1"/>
     <col min="7" max="7" width="72.35" style="5" customWidth="1"/>
     <col min="8" max="8" width="48.525" style="4" customWidth="1"/>
     <col min="9" max="9" width="12.875" style="4" customWidth="1"/>
@@ -1604,7 +1429,7 @@
     <col min="12" max="12" width="20.8833333333333" style="7" customWidth="1"/>
     <col min="13" max="13" width="21.175" style="7" customWidth="1"/>
     <col min="14" max="16" width="12.875" style="8" customWidth="1"/>
-    <col min="17" max="17" width="72.125" style="5" customWidth="1"/>
+    <col min="17" max="17" width="12.5" style="5" customWidth="1"/>
     <col min="18" max="18" width="9.375" style="5"/>
     <col min="19" max="19" width="19.875" style="5" customWidth="1"/>
     <col min="20" max="20" width="13.75" style="5" customWidth="1"/>
@@ -1614,81 +1439,86 @@
     <col min="24" max="16384" width="9" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" s="2" customFormat="1" ht="15" spans="1:17">
-      <c r="A1" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="9" t="s">
+    <row r="1" spans="1:18">
+      <c r="A1" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="9" t="s">
+      <c r="C1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="9" t="s">
+      <c r="D1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="9" t="s">
+      <c r="E1" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="10" t="s">
+      <c r="F1" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="9" t="s">
+      <c r="H1" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="11" t="s">
+      <c r="I1" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="12" t="s">
+      <c r="J1" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="9" t="s">
+      <c r="K1" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="9" t="s">
+      <c r="L1" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="13" t="s">
+      <c r="M1" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="13" t="s">
+      <c r="N1" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="14" t="s">
+      <c r="O1" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="14" t="s">
+      <c r="P1" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="14" t="s">
+      <c r="Q1" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" s="2" customFormat="1" ht="15" spans="1:17">
+      <c r="R1" s="5" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" s="2" customFormat="1" ht="15" spans="1:18">
       <c r="A2" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="B2" s="15" t="s">
+      <c r="B2" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="C2" s="16"/>
-      <c r="D2" s="9"/>
-      <c r="E2" s="9" t="s">
+      <c r="C2" s="9"/>
+      <c r="D2" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="F2" s="15" t="s">
+      <c r="E2" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="G2" s="15" t="s">
+      <c r="F2" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="G2" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="H2" s="12" t="s">
+      <c r="H2" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="I2" s="12" t="s">
+      <c r="I2" s="11" t="s">
         <v>20</v>
       </c>
       <c r="J2" s="9" t="s">
@@ -1697,23 +1527,26 @@
       <c r="K2" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="L2" s="13" t="s">
+      <c r="L2" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="M2" s="13" t="s">
+      <c r="M2" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="N2" s="14" t="s">
+      <c r="N2" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="O2" s="14" t="s">
+      <c r="O2" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="P2" s="14" t="s">
+      <c r="P2" s="13" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" s="2" customFormat="1" ht="15" spans="1:17">
+      <c r="Q2" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="3" s="2" customFormat="1" ht="15" spans="1:18">
       <c r="A3" s="9" t="s">
         <v>22</v>
       </c>
@@ -1721,486 +1554,548 @@
         <v>23</v>
       </c>
       <c r="C3" s="9"/>
-      <c r="D3" s="9"/>
-      <c r="E3" s="9" t="s">
+      <c r="D3" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="F3" s="10" t="s">
+      <c r="E3" s="14" t="s">
         <v>25</v>
       </c>
+      <c r="F3" s="14" t="s">
+        <v>26</v>
+      </c>
       <c r="G3" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H3" s="11" t="s">
         <v>27</v>
       </c>
-      <c r="I3" s="12" t="s">
+      <c r="H3" s="15" t="s">
         <v>28</v>
       </c>
+      <c r="I3" s="11" t="s">
+        <v>29</v>
+      </c>
       <c r="J3" s="9" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K3" s="9" t="s">
-        <v>30</v>
-      </c>
-      <c r="L3" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="M3" s="13" t="s">
+      <c r="L3" s="12" t="s">
         <v>32</v>
       </c>
-      <c r="N3" s="14" t="s">
+      <c r="M3" s="12" t="s">
         <v>33</v>
       </c>
-      <c r="O3" s="14" t="s">
+      <c r="N3" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="P3" s="14" t="s">
+      <c r="O3" s="13" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="4" s="2" customFormat="1" ht="15" spans="1:17">
+      <c r="P3" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q3" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="4" s="2" customFormat="1" ht="15" spans="1:18">
       <c r="A4" s="9"/>
       <c r="B4" s="9"/>
       <c r="C4" s="9"/>
       <c r="D4" s="9"/>
-      <c r="E4" s="9"/>
-      <c r="F4" s="10"/>
+      <c r="E4" s="14"/>
+      <c r="F4" s="14"/>
       <c r="G4" s="9"/>
-      <c r="H4" s="12"/>
-      <c r="I4" s="12"/>
+      <c r="H4" s="11"/>
+      <c r="I4" s="11"/>
       <c r="J4" s="9"/>
       <c r="K4" s="9"/>
-      <c r="L4" s="13"/>
-      <c r="M4" s="13"/>
-      <c r="N4" s="14"/>
-      <c r="O4" s="14"/>
-      <c r="P4" s="14"/>
-    </row>
-    <row r="5" spans="1:17">
+      <c r="L4" s="12"/>
+      <c r="M4" s="12"/>
+      <c r="N4" s="13"/>
+      <c r="O4" s="13"/>
+      <c r="P4" s="13"/>
+    </row>
+    <row r="5" spans="1:18">
       <c r="A5" s="5">
         <v>1</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="D5" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="E5" s="5">
-        <v>3</v>
+        <v>38</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="D5" s="5">
+        <v>2</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="I5" s="17" t="b">
+        <v>41</v>
+      </c>
+      <c r="I5" s="16" t="b">
         <v>1</v>
       </c>
-      <c r="J5" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="K5" s="17" t="b">
+      <c r="J5" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="K5" s="16" t="b">
         <v>1</v>
       </c>
-      <c r="L5" s="26" t="s">
-        <v>40</v>
-      </c>
-      <c r="M5" s="26" t="s">
-        <v>41</v>
+      <c r="L5" s="25" t="s">
+        <v>42</v>
+      </c>
+      <c r="M5" s="25" t="s">
+        <v>43</v>
       </c>
       <c r="N5" s="8">
-        <v>3</v>
-      </c>
-      <c r="Q5" s="5" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="6" s="3" customFormat="1" spans="1:17">
+        <v>99</v>
+      </c>
+      <c r="Q5" s="5">
+        <v>0</v>
+      </c>
+      <c r="R5" s="5" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="6" s="3" customFormat="1" spans="1:18">
       <c r="A6" s="3">
         <v>2</v>
       </c>
       <c r="B6" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="D6" s="3">
+        <v>3</v>
+      </c>
+      <c r="E6" s="18"/>
+      <c r="F6" s="18"/>
+      <c r="G6" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="H6" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="I6" s="16" t="b">
+        <v>1</v>
+      </c>
+      <c r="J6" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="K6" s="16" t="b">
+        <v>1</v>
+      </c>
+      <c r="L6" s="26" t="s">
+        <v>42</v>
+      </c>
+      <c r="M6" s="26" t="s">
         <v>43</v>
       </c>
-      <c r="D6" s="3" t="s">
+      <c r="N6" s="8">
+        <v>99</v>
+      </c>
+      <c r="O6" s="20"/>
+      <c r="P6" s="20"/>
+      <c r="Q6" s="3">
+        <v>0</v>
+      </c>
+      <c r="R6" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="E6" s="3">
-        <v>4</v>
-      </c>
-      <c r="F6" s="19" t="s">
-        <v>45</v>
-      </c>
-      <c r="G6" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="H6" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="I6" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="J6" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="K6" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="L6" s="27" t="s">
-        <v>40</v>
-      </c>
-      <c r="M6" s="27" t="s">
-        <v>41</v>
-      </c>
-      <c r="N6" s="21">
-        <v>1</v>
-      </c>
-      <c r="O6" s="21"/>
-      <c r="P6" s="21"/>
-      <c r="Q6" s="3" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="7" s="4" customFormat="1" spans="1:17">
+    </row>
+    <row r="7" s="4" customFormat="1" spans="1:18">
       <c r="A7" s="4">
         <v>3</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="D7" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="E7" s="4">
-        <v>5</v>
-      </c>
-      <c r="F7" s="22"/>
+      <c r="C7" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="D7" s="4">
+        <v>4</v>
+      </c>
+      <c r="E7" s="21"/>
+      <c r="F7" s="21"/>
       <c r="G7" s="4" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H7" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="I7" s="17" t="b">
+        <v>52</v>
+      </c>
+      <c r="I7" s="16" t="b">
         <v>1</v>
       </c>
-      <c r="J7" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="K7" s="17" t="b">
+      <c r="J7" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="K7" s="16" t="b">
         <v>1</v>
       </c>
-      <c r="L7" s="28" t="s">
-        <v>40</v>
-      </c>
-      <c r="M7" s="28" t="s">
-        <v>41</v>
-      </c>
-      <c r="N7" s="24">
-        <v>5</v>
-      </c>
-      <c r="O7" s="24"/>
-      <c r="P7" s="24"/>
-      <c r="Q7" s="4" t="s">
+      <c r="L7" s="27" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="8" s="3" customFormat="1" spans="1:17">
+      <c r="M7" s="27" t="s">
+        <v>43</v>
+      </c>
+      <c r="N7" s="8">
+        <v>99</v>
+      </c>
+      <c r="O7" s="23"/>
+      <c r="P7" s="23"/>
+      <c r="Q7" s="4">
+        <v>0</v>
+      </c>
+      <c r="R7" s="4" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="8" s="3" customFormat="1" spans="1:18">
       <c r="A8" s="3">
         <v>4</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="D8" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="E8" s="3">
-        <v>6</v>
-      </c>
-      <c r="F8" s="19"/>
+      <c r="C8" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="D8" s="3"/>
+      <c r="E8" s="18"/>
+      <c r="F8" s="18"/>
       <c r="G8" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="I8" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="J8" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="K8" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="L8" s="27" t="s">
-        <v>40</v>
-      </c>
-      <c r="M8" s="27" t="s">
-        <v>41</v>
-      </c>
-      <c r="N8" s="21">
+        <v>56</v>
+      </c>
+      <c r="I8" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="J8" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="K8" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="L8" s="26" t="s">
+        <v>42</v>
+      </c>
+      <c r="M8" s="26" t="s">
+        <v>43</v>
+      </c>
+      <c r="N8" s="20">
         <v>3</v>
       </c>
-      <c r="O8" s="21"/>
-      <c r="P8" s="21"/>
-      <c r="Q8" s="3" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="9" s="3" customFormat="1" spans="1:17">
+      <c r="O8" s="20"/>
+      <c r="P8" s="20"/>
+      <c r="Q8" s="3">
+        <v>0</v>
+      </c>
+      <c r="R8" s="3" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="9" s="3" customFormat="1" spans="1:18">
       <c r="A9" s="3">
         <v>5</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="D9" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="E9" s="3">
-        <v>7</v>
-      </c>
-      <c r="F9" s="19" t="s">
+      <c r="C9" s="3" t="s">
         <v>58</v>
       </c>
+      <c r="D9" s="3"/>
+      <c r="E9" s="18"/>
+      <c r="F9" s="18"/>
       <c r="G9" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="H9" s="18" t="s">
+      <c r="H9" s="17" t="s">
         <v>60</v>
       </c>
-      <c r="I9" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="J9" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="K9" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="L9" s="27" t="s">
-        <v>40</v>
-      </c>
-      <c r="M9" s="27" t="s">
-        <v>40</v>
-      </c>
-      <c r="N9" s="21">
+      <c r="I9" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="J9" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="K9" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="L9" s="26" t="s">
+        <v>42</v>
+      </c>
+      <c r="M9" s="26" t="s">
+        <v>43</v>
+      </c>
+      <c r="N9" s="20">
         <v>2</v>
       </c>
-      <c r="O9" s="21"/>
-      <c r="P9" s="21"/>
-      <c r="Q9" s="3" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="10" s="3" customFormat="1" spans="1:17">
+      <c r="O9" s="20"/>
+      <c r="P9" s="20"/>
+      <c r="Q9" s="3">
+        <v>0</v>
+      </c>
+      <c r="R9" s="3" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="10" s="3" customFormat="1" spans="1:18">
       <c r="A10" s="3">
         <v>6</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="D10" s="3" t="s">
+      <c r="C10" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="E10" s="3">
-        <v>8</v>
-      </c>
-      <c r="F10" s="19"/>
+      <c r="D10" s="3"/>
+      <c r="E10" s="18"/>
+      <c r="F10" s="18"/>
       <c r="G10" s="3"/>
       <c r="H10" s="3"/>
-      <c r="I10" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="J10" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="K10" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="L10" s="27" t="s">
-        <v>40</v>
-      </c>
-      <c r="M10" s="27" t="s">
+      <c r="I10" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="J10" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="K10" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="L10" s="26" t="s">
+        <v>42</v>
+      </c>
+      <c r="M10" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="N10" s="21">
+      <c r="N10" s="20">
         <v>1</v>
       </c>
-      <c r="O10" s="21"/>
-      <c r="P10" s="21"/>
-      <c r="Q10" s="3" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="11" s="3" customFormat="1" spans="1:17">
+      <c r="O10" s="20"/>
+      <c r="P10" s="20"/>
+      <c r="Q10" s="3">
+        <v>0</v>
+      </c>
+      <c r="R10" s="3" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="11" s="3" customFormat="1" spans="1:18">
       <c r="A11" s="3">
         <v>7</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="D11" s="3" t="s">
+      <c r="C11" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="E11" s="3">
-        <v>9</v>
-      </c>
-      <c r="F11" s="19"/>
+      <c r="D11" s="3"/>
+      <c r="E11" s="18"/>
+      <c r="F11" s="18"/>
       <c r="G11" s="3" t="s">
         <v>66</v>
       </c>
       <c r="H11" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="I11" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="J11" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="K11" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="L11" s="27" t="s">
-        <v>40</v>
-      </c>
-      <c r="M11" s="27" t="s">
-        <v>63</v>
-      </c>
-      <c r="N11" s="21">
-        <v>3</v>
-      </c>
-      <c r="O11" s="21"/>
-      <c r="P11" s="21"/>
-      <c r="Q11" s="3" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="12" s="3" customFormat="1" spans="1:17">
+      <c r="I11" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="J11" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="K11" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="L11" s="26" t="s">
+        <v>68</v>
+      </c>
+      <c r="M11" s="26" t="s">
+        <v>43</v>
+      </c>
+      <c r="N11" s="8">
+        <v>99</v>
+      </c>
+      <c r="O11" s="20"/>
+      <c r="P11" s="20"/>
+      <c r="Q11" s="3">
+        <v>1</v>
+      </c>
+      <c r="R11" s="3" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="12" s="3" customFormat="1" spans="1:18">
       <c r="A12" s="3">
         <v>8</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="D12" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="E12" s="3">
-        <v>10</v>
-      </c>
-      <c r="F12" s="19"/>
+      <c r="C12" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="D12" s="3"/>
+      <c r="E12" s="18"/>
+      <c r="F12" s="18"/>
       <c r="G12" s="3"/>
       <c r="H12" s="3"/>
-      <c r="I12" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="J12" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="K12" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="L12" s="27" t="s">
-        <v>40</v>
-      </c>
-      <c r="M12" s="27" t="s">
-        <v>41</v>
-      </c>
-      <c r="N12" s="21">
+      <c r="I12" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="J12" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="K12" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="L12" s="26" t="s">
+        <v>42</v>
+      </c>
+      <c r="M12" s="26" t="s">
+        <v>43</v>
+      </c>
+      <c r="N12" s="20">
         <v>1</v>
       </c>
-      <c r="O12" s="21"/>
-      <c r="P12" s="21"/>
-      <c r="Q12" s="3" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="13" s="3" customFormat="1" spans="1:17">
+      <c r="O12" s="20"/>
+      <c r="P12" s="20"/>
+      <c r="Q12" s="3">
+        <v>0</v>
+      </c>
+      <c r="R12" s="3" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="13" s="3" customFormat="1" spans="1:18">
       <c r="A13" s="3">
         <v>9</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="D13" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="E13" s="3">
-        <v>2</v>
-      </c>
-      <c r="F13" s="19" t="s">
+      <c r="C13" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="G13" s="19"/>
+      <c r="D13" s="3"/>
+      <c r="E13" s="18"/>
+      <c r="F13" s="18"/>
+      <c r="G13" s="18"/>
       <c r="H13" s="3"/>
-      <c r="I13" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="J13" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="K13" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="L13" s="27" t="s">
+      <c r="I13" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="J13" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="K13" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="L13" s="26" t="s">
+        <v>68</v>
+      </c>
+      <c r="M13" s="26" t="s">
         <v>73</v>
       </c>
-      <c r="M13" s="27" t="s">
+      <c r="N13" s="20">
+        <v>99</v>
+      </c>
+      <c r="O13" s="24"/>
+      <c r="P13" s="18"/>
+      <c r="Q13" s="3">
+        <v>0</v>
+      </c>
+      <c r="R13" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="N13" s="21">
-        <v>99</v>
-      </c>
-      <c r="O13" s="25"/>
-      <c r="P13" s="19"/>
-      <c r="Q13" s="3" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="14" s="4" customFormat="1" spans="1:17">
+    </row>
+    <row r="14" s="4" customFormat="1" spans="1:18">
       <c r="A14" s="4">
         <v>10</v>
       </c>
       <c r="B14" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="C14" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="D14" s="4" t="s">
+      <c r="D14" s="4">
+        <v>1</v>
+      </c>
+      <c r="E14" s="21"/>
+      <c r="F14" s="21"/>
+      <c r="G14" s="4"/>
+      <c r="I14" s="16" t="b">
+        <v>1</v>
+      </c>
+      <c r="J14" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="K14" s="16" t="b">
+        <v>1</v>
+      </c>
+      <c r="L14" s="27" t="s">
+        <v>68</v>
+      </c>
+      <c r="M14" s="27" t="s">
         <v>77</v>
       </c>
-      <c r="E14" s="4">
-        <v>1</v>
-      </c>
-      <c r="F14" s="22"/>
-      <c r="G14" s="4"/>
-      <c r="I14" s="17" t="b">
-        <v>1</v>
-      </c>
-      <c r="J14" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="K14" s="17" t="b">
-        <v>1</v>
-      </c>
-      <c r="L14" s="28" t="s">
-        <v>73</v>
-      </c>
-      <c r="M14" s="28" t="s">
+      <c r="N14" s="23">
+        <v>99</v>
+      </c>
+      <c r="O14" s="23"/>
+      <c r="P14" s="23"/>
+      <c r="Q14" s="4">
+        <v>0</v>
+      </c>
+      <c r="R14" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="N14" s="24">
+    </row>
+    <row r="15" spans="1:18">
+      <c r="A15" s="5">
+        <v>11</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="I15" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="J15" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="K15" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="L15" s="26" t="s">
+        <v>68</v>
+      </c>
+      <c r="M15" s="26" t="s">
+        <v>43</v>
+      </c>
+      <c r="N15" s="8">
         <v>99</v>
       </c>
-      <c r="O14" s="24"/>
-      <c r="P14" s="24"/>
-      <c r="Q14" s="4" t="s">
-        <v>79</v>
+      <c r="O15" s="8"/>
+      <c r="Q15" s="5">
+        <v>0</v>
+      </c>
+      <c r="R15" s="5" t="s">
+        <v>74</v>
       </c>
     </row>
   </sheetData>
@@ -2210,7 +2105,6 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>
-  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
 
@@ -2225,42 +2119,42 @@
   <sheetData>
     <row r="1" spans="1:16">
       <c r="A1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="2" spans="1:16">
       <c r="A2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="3" spans="1:16">
       <c r="A3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="4" spans="1:16">
       <c r="A4" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="5" spans="1:16">
       <c r="A5" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="6" spans="1:16">
       <c r="A6" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="7" spans="1:16">
       <c r="A7" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="9" spans="1:16">
       <c r="A9" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B9" s="1"/>
       <c r="C9" s="1"/>
@@ -2283,20 +2177,20 @@
         <v>1</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D10" s="1">
         <v>1</v>
       </c>
       <c r="E10" s="1"/>
       <c r="F10" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="H10" s="1"/>
       <c r="I10" s="1"/>
@@ -2313,20 +2207,20 @@
         <v>2</v>
       </c>
       <c r="B11" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="C11" s="1" t="s">
         <v>89</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>90</v>
       </c>
       <c r="D11" s="1">
         <v>2</v>
       </c>
       <c r="E11" s="1"/>
       <c r="F11" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="G11" s="1" t="s">
         <v>91</v>
-      </c>
-      <c r="G11" s="1" t="s">
-        <v>92</v>
       </c>
       <c r="H11" s="1"/>
       <c r="I11" s="1"/>
@@ -2343,20 +2237,20 @@
         <v>3</v>
       </c>
       <c r="B12" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="C12" s="1" t="s">
         <v>93</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>94</v>
       </c>
       <c r="D12" s="1">
         <v>4</v>
       </c>
       <c r="E12" s="1"/>
       <c r="F12" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="G12" s="1" t="s">
         <v>95</v>
-      </c>
-      <c r="G12" s="1" t="s">
-        <v>96</v>
       </c>
       <c r="H12" s="1"/>
       <c r="I12" s="1"/>
@@ -2373,20 +2267,20 @@
         <v>4</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D13" s="1">
         <v>5</v>
       </c>
       <c r="E13" s="1"/>
       <c r="F13" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="G13" s="1" t="s">
         <v>98</v>
-      </c>
-      <c r="G13" s="1" t="s">
-        <v>99</v>
       </c>
       <c r="H13" s="1"/>
       <c r="I13" s="1"/>
@@ -2403,22 +2297,22 @@
         <v>5</v>
       </c>
       <c r="B14" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="C14" s="1" t="s">
         <v>100</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>101</v>
       </c>
       <c r="D14" s="1">
         <v>3</v>
       </c>
       <c r="E14" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="F14" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="F14" s="1" t="s">
+      <c r="G14" s="1" t="s">
         <v>103</v>
-      </c>
-      <c r="G14" s="1" t="s">
-        <v>104</v>
       </c>
       <c r="H14" s="1"/>
       <c r="I14" s="1"/>
